--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,7 @@
     <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
   </si>
   <si>
-    <t>435: fixed value = finished when PTF - DISCHARGE DATE (#45-70) case not null</t>
+    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (#45-70) case not null</t>
   </si>
   <si>
     <t>Inpat.Census.CensusDateTime
@@ -824,6 +824,12 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ActCode"/&gt;
+  &lt;code value="IMP"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Classification of the encounter.</t>
   </si>
   <si>
@@ -839,7 +845,7 @@
     <t>PV1-2</t>
   </si>
   <si>
-    <t>1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode|IMP</t>
+    <t>1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode#IMP</t>
   </si>
   <si>
     <t>Encounter.classHistory</t>
@@ -5633,7 +5639,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5651,10 +5657,10 @@
         <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5690,16 +5696,16 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5707,10 +5713,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5736,10 +5742,10 @@
         <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5790,7 +5796,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5825,10 +5831,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5943,10 +5949,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6063,10 +6069,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6185,10 +6191,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6214,10 +6220,10 @@
         <v>251</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6247,10 +6253,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6268,7 +6274,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6303,10 +6309,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6332,10 +6338,10 @@
         <v>208</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6386,7 +6392,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6421,10 +6427,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6450,13 +6456,13 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6485,10 +6491,10 @@
         <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6506,7 +6512,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6521,30 +6527,30 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6570,10 +6576,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6600,13 +6606,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6624,7 +6630,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6639,7 +6645,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>160</v>
@@ -6648,7 +6654,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6659,10 +6665,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6688,10 +6694,10 @@
         <v>178</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6718,13 +6724,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6742,7 +6748,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6760,13 +6766,13 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6777,14 +6783,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6803,16 +6809,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6862,7 +6868,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6877,30 +6883,30 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6923,13 +6929,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6980,7 +6986,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6995,16 +7001,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7015,14 +7021,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7041,13 +7047,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7098,7 +7104,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7113,10 +7119,10 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
@@ -7133,10 +7139,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7162,10 +7168,10 @@
         <v>235</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7216,7 +7222,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7231,16 +7237,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7251,10 +7257,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7369,10 +7375,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7489,10 +7495,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7611,10 +7617,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7640,13 +7646,13 @@
         <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7675,10 +7681,10 @@
         <v>183</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7696,7 +7702,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7711,16 +7717,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7731,10 +7737,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7760,10 +7766,10 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7814,7 +7820,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7832,13 +7838,13 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7849,10 +7855,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7875,13 +7881,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7932,7 +7938,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7947,19 +7953,19 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7967,10 +7973,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7993,13 +7999,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8050,7 +8056,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8065,16 +8071,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8085,10 +8091,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8114,13 +8120,13 @@
         <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8170,7 +8176,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8185,16 +8191,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8205,10 +8211,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8323,10 +8329,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8443,10 +8449,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8469,16 +8475,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8528,7 +8534,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8537,7 +8543,7 @@
         <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>102</v>
@@ -8546,27 +8552,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8589,23 +8595,23 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>82</v>
@@ -8650,7 +8656,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8659,7 +8665,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8668,16 +8674,16 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>233</v>
@@ -8685,10 +8691,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8711,16 +8717,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8770,7 +8776,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8785,16 +8791,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8805,14 +8811,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8834,13 +8840,13 @@
         <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8869,10 +8875,10 @@
         <v>114</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8890,7 +8896,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8905,34 +8911,34 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8951,16 +8957,16 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9010,7 +9016,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9025,16 +9031,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9045,10 +9051,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9074,10 +9080,10 @@
         <v>235</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9128,7 +9134,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9146,7 +9152,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -9163,10 +9169,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9281,10 +9287,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9401,10 +9407,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9523,14 +9529,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9549,16 +9555,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9608,7 +9614,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -9623,19 +9629,19 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9643,10 +9649,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9672,10 +9678,10 @@
         <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9705,10 +9711,10 @@
         <v>114</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9726,7 +9732,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9761,10 +9767,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9787,13 +9793,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9844,7 +9850,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9862,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
@@ -9879,10 +9885,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9905,16 +9911,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9964,7 +9970,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9982,7 +9988,7 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9999,10 +10005,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10028,13 +10034,13 @@
         <v>235</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10084,7 +10090,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10102,7 +10108,7 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>82</v>
@@ -10119,10 +10125,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10237,10 +10243,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10357,10 +10363,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10479,10 +10485,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10508,10 +10514,10 @@
         <v>148</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10562,7 +10568,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10586,7 +10592,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10597,10 +10603,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10623,13 +10629,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10680,7 +10686,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10698,7 +10704,7 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -10715,10 +10721,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10833,10 +10839,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10953,10 +10959,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10982,13 +10988,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11038,7 +11044,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11047,7 +11053,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11073,10 +11079,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11102,13 +11108,13 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11137,10 +11143,10 @@
         <v>183</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11158,7 +11164,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11193,10 +11199,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11222,13 +11228,13 @@
         <v>148</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11278,7 +11284,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11296,7 +11302,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -11313,10 +11319,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11342,13 +11348,13 @@
         <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11398,7 +11404,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11425,18 +11431,18 @@
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11462,10 +11468,10 @@
         <v>178</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11495,10 +11501,10 @@
         <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11516,7 +11522,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11534,13 +11540,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11551,10 +11557,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11669,10 +11675,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11789,10 +11795,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11818,16 +11824,16 @@
         <v>251</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11856,7 +11862,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11874,7 +11880,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11892,27 +11898,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12027,10 +12033,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12147,10 +12153,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12176,16 +12182,16 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12234,7 +12240,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12252,13 +12258,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12269,10 +12275,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12298,13 +12304,13 @@
         <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12354,7 +12360,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12372,13 +12378,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12389,10 +12395,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12418,14 +12424,14 @@
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12474,7 +12480,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12492,27 +12498,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12538,14 +12544,14 @@
         <v>156</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12594,7 +12600,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12612,13 +12618,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12629,10 +12635,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12655,19 +12661,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12716,7 +12722,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12734,13 +12740,13 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12751,10 +12757,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12780,16 +12786,16 @@
         <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12838,7 +12844,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12856,13 +12862,13 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12873,10 +12879,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12902,10 +12908,10 @@
         <v>178</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12932,13 +12938,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12956,7 +12962,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12980,7 +12986,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12991,10 +12997,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13020,16 +13026,16 @@
         <v>178</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13054,13 +13060,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13078,7 +13084,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13096,13 +13102,13 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13113,10 +13119,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13142,10 +13148,10 @@
         <v>178</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13175,10 +13181,10 @@
         <v>114</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13196,7 +13202,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13214,13 +13220,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13231,10 +13237,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13260,10 +13266,10 @@
         <v>178</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13293,10 +13299,10 @@
         <v>114</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13314,7 +13320,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13332,13 +13338,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13349,10 +13355,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13375,13 +13381,13 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13432,7 +13438,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13450,13 +13456,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13467,10 +13473,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13585,10 +13591,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13705,10 +13711,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13734,13 +13740,13 @@
         <v>156</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13790,7 +13796,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13799,7 +13805,7 @@
         <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
@@ -13825,10 +13831,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13854,13 +13860,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13889,10 +13895,10 @@
         <v>183</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13910,7 +13916,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13945,10 +13951,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13974,13 +13980,13 @@
         <v>148</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14030,7 +14036,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14048,7 +14054,7 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>82</v>
@@ -14065,10 +14071,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14094,13 +14100,13 @@
         <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14150,7 +14156,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14177,18 +14183,18 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14214,10 +14220,10 @@
         <v>178</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14247,10 +14253,10 @@
         <v>114</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14268,7 +14274,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14286,27 +14292,27 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14332,13 +14338,13 @@
         <v>235</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14388,7 +14394,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14406,7 +14412,7 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>82</v>
@@ -14423,10 +14429,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14541,10 +14547,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14661,10 +14667,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14783,10 +14789,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14809,13 +14815,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14866,7 +14872,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>90</v>
@@ -14881,30 +14887,30 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14930,13 +14936,13 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14965,10 +14971,10 @@
         <v>172</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14986,7 +14992,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15004,7 +15010,7 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
@@ -15021,10 +15027,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15050,13 +15056,13 @@
         <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15082,13 +15088,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15106,7 +15112,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15141,10 +15147,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15170,10 +15176,10 @@
         <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15224,7 +15230,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15242,7 +15248,7 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
@@ -15259,10 +15265,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15285,13 +15291,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15342,7 +15348,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15357,30 +15363,30 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15403,16 +15409,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15462,7 +15468,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15477,10 +15483,10 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,9 +656,7 @@
     <t>428: source value from PTF - INTERNAL ADMISSION # (#45-2.1)</t>
   </si>
   <si>
-    <t>Inpat.Census.AdmitEligibilityIEN
-Inpat.Inpatient.AdmitEligibilityIEN
-Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
+    <t>Inpat.Census.AdmitEligibilityIEN,Inpat.Inpatient.AdmitEligibilityIEN,Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
   </si>
   <si>
     <t>Encounter.identifier.period</t>
@@ -741,23 +739,7 @@
     <t>435: fixed value = #finished when PTF - DISCHARGE DATE (#45-70) case not null</t>
   </si>
   <si>
-    <t>Inpat.Census.CensusDateTime
-Inpat.Census501.CensusDateTime
-Inpat.Census501Diagnosis.CensusDateTime
-Inpat.Census535.CensusDateTime
-Inpat.CensusDiagnosis.CensusDateTime
-Inpat.CensusICDProcedure.CensusDateTime
-Inpat.CensusSurgicalProcedure.CensusDateTime
-Inpat.Inpatient.DischargeDateTime
-Inpat.Inpatient501Transaction.DischargeDateTime
-Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime
-Inpat.Inpatient535Multiple.DischargeDateTime
-Inpat.Inpatient535Transaction.DischargeDateTime
-Inpat.InpatientDiagnosis.DischargeDateTime
-Inpat.InpatientFeeBasis.DischargeDateTime
-Inpat.InpatientFeeDiagnosis.DischargeDateTime
-Inpat.InpatientICDProcedure.DischargeDateTime
-Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
+    <t>Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
   </si>
   <si>
     <t>Encounter.statusHistory</t>
@@ -994,20 +976,7 @@
     <t>441: source value from PTF - PATIENT (#45-.01)</t>
   </si>
   <si>
-    <t>Inpat.Census.PatientIEN
-Inpat.Census501.PatientIEN
-Inpat.Census535.PatientIEN
-Inpat.CensusICDProcedure.PatientIEN
-Inpat.CensusSurgicalProcedure.PatientIEN
-Inpat.Inpatient.PatientIEN
-Inpat.Inpatient501Transaction.PatientIEN
-Inpat.Inpatient535Transaction.PatientIEN
-Inpat.InpatientDiagnosis.PatientIEN
-Inpat.InpatientDischargeDiagnosis.PatientIEN
-Inpat.InpatientFeeBasis.PatientIEN
-Inpat.InpatientICDProcedure.PatientIEN
-Inpat.InpatientSurgicalProcedure.PatientIEN
-Inpat.PresentOnAdmission.PatientIEN</t>
+    <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census535.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
   </si>
   <si>
     <t>Encounter.episodeOfCare</t>
@@ -1230,23 +1199,7 @@
     <t>445: source value from PTF - ADMISSION DATE (#45-2)</t>
   </si>
   <si>
-    <t>Inpat.Census.AdmitDateTime
-Inpat.Census501.AdmitDateTime
-Inpat.Census501Diagnosis.AdmitDateTime
-Inpat.Census535.AdmitDateTime
-Inpat.CensusDiagnosis.AdmitDateTime
-Inpat.CensusICDProcedure.AdmitDateTime
-Inpat.CensusSurgicalProcedure.AdmitDateTime
-Inpat.Inpatient.AdmitDateTime
-Inpat.Inpatient501Multiple.AdmitDateTime
-Inpat.Inpatient501Transaction.AdmitDateTime
-Inpat.Inpatient535Multiple.AdmitDateTime
-Inpat.Inpatient535Transaction.AdmitDateTime
-Inpat.InpatientDischargeDiagnosis.AdmitDateTime
-Inpat.InpatientFeeBasis.AdmitDateTime
-Inpat.InpatientFeeDiagnosis.AdmitDateTime
-Inpat.InpatientICDProcedure.AdmitDateTime
-Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
+    <t>Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
   </si>
   <si>
     <t>Encounter.period.end</t>
@@ -1588,9 +1541,7 @@
     <t>454: source value from PTF - TRANSFERRING FACILITY (#45-21.1)</t>
   </si>
   <si>
-    <t>Inpat.Census.TransferringFacility
-Inpat.Inpatient.TransferFromFacility
-Inpat.InpatientFeeBasis.TransferringFacility</t>
+    <t>Inpat.Census.TransferringFacility,Inpat.Inpatient.TransferFromFacility,Inpat.InpatientFeeBasis.TransferringFacility</t>
   </si>
   <si>
     <t>Encounter.hospitalization.admitSource</t>
@@ -1650,9 +1601,8 @@
     <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
-    <t>Inpat.Census.AdmitSourceIEN
-Inpat.Inpatient.AdmitSourceIEN
-Inpat.InpatientFeeBasis.AdmitSourceIEN</t>
+    <t>Inpat.Census.AdmitSourceIEN,Inpat.Inpatient.AdmitSourceIEN,Inpat.InpatientFeeBasis.AdmitSourceIEN
+Dim.AdmitSource.AdmitSourceCode</t>
   </si>
   <si>
     <t>Encounter.hospitalization.admitSource.coding.id</t>
@@ -1926,9 +1876,7 @@
     <t>455: source value from PTF - RECEIVING FACILITY (#45-76.1)</t>
   </si>
   <si>
-    <t>Inpat.Census.ReceivingFacility
-Inpat.Inpatient.TransferToFacility
-Inpat.InpatientFeeBasis.ReceivingFacility</t>
+    <t>Inpat.Census.ReceivingFacility,Inpat.Inpatient.TransferToFacility,Inpat.InpatientFeeBasis.ReceivingFacility</t>
   </si>
   <si>
     <t>Encounter.hospitalization.dischargeDisposition</t>
@@ -1955,9 +1903,7 @@
     <t>456: source value from PTF - PLACE OF DISPOSITION (#45-75)</t>
   </si>
   <si>
-    <t>Inpat.Census.PlaceOfDispositionIEN
-Inpat.Inpatient.PlaceOfDispositionIEN
-Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
+    <t>Inpat.Census.PlaceOfDispositionIEN,Inpat.Inpatient.PlaceOfDispositionIEN,Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
   </si>
   <si>
     <t>Encounter.location</t>
@@ -2009,9 +1955,7 @@
     <t>461: reference from PTF - FACILITY (#45-3)</t>
   </si>
   <si>
-    <t>Inpat.Census.DischargeFacility
-Inpat.Inpatient.DischargeFromFacility
-Inpat.InpatientFeeBasis.DischargeFacility</t>
+    <t>Inpat.Census.DischargeFacility,Inpat.Inpatient.DischargeFromFacility,Inpat.InpatientFeeBasis.DischargeFacility</t>
   </si>
   <si>
     <t>Encounter.location.status</t>
@@ -2466,7 +2410,7 @@
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="110.4140625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="56.453125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t xml:space="preserve">Visit
@@ -647,16 +647,16 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>428: source value from PTF - INTERNAL ADMISSION # (#45-2.1)</t>
+  </si>
+  <si>
+    <t>Inpat.Census.AdmitEligibilityIEN,Inpat.Inpatient.AdmitEligibilityIEN,Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>428: source value from PTF - INTERNAL ADMISSION # (#45-2.1)</t>
-  </si>
-  <si>
-    <t>Inpat.Census.AdmitEligibilityIEN,Inpat.Inpatient.AdmitEligibilityIEN,Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
   </si>
   <si>
     <t>Encounter.identifier.period</t>
@@ -724,6 +724,12 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
   </si>
   <si>
+    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (#45-70) case not null</t>
+  </si>
+  <si>
+    <t>Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -734,12 +740,6 @@
   </si>
   <si>
     <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
-  </si>
-  <si>
-    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (#45-70) case not null</t>
-  </si>
-  <si>
-    <t>Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
   </si>
   <si>
     <t>Encounter.statusHistory</t>
@@ -818,6 +818,9 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
+    <t>1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode#IMP</t>
+  </si>
+  <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
   </si>
   <si>
@@ -827,9 +830,6 @@
     <t>PV1-2</t>
   </si>
   <si>
-    <t>1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode#IMP</t>
-  </si>
-  <si>
     <t>Encounter.classHistory</t>
   </si>
   <si>
@@ -884,6 +884,12 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-encounter-type</t>
   </si>
   <si>
+    <t>1616: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT (#46-.01 &gt; 81-)</t>
+  </si>
+  <si>
+    <t>Inpat.InpatientCPTProcedure.CPTIEN</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -891,12 +897,6 @@
   </si>
   <si>
     <t>PV1-4 / PV1-18</t>
-  </si>
-  <si>
-    <t>1616: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT (#46-.01 &gt; 81-)</t>
-  </si>
-  <si>
-    <t>Inpat.InpatientCPTProcedure.CPTIEN</t>
   </si>
   <si>
     <t>Encounter.serviceType</t>
@@ -961,6 +961,12 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
+    <t>441: source value from PTF - PATIENT (#45-.01)</t>
+  </si>
+  <si>
+    <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census535.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -971,12 +977,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>441: source value from PTF - PATIENT (#45-.01)</t>
-  </si>
-  <si>
-    <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census535.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
   </si>
   <si>
     <t>Encounter.episodeOfCare</t>
@@ -1103,6 +1103,9 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
+    <t>442: reference from PTF - PROVIDER (#45-79.1)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1113,9 +1116,6 @@
   </si>
   <si>
     <t>ROL-4</t>
-  </si>
-  <si>
-    <t>442: reference from PTF - PROVIDER (#45-79.1)</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -1190,18 +1190,18 @@
 </t>
   </si>
   <si>
+    <t>445: source value from PTF - ADMISSION DATE (#45-2)</t>
+  </si>
+  <si>
+    <t>Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>445: source value from PTF - ADMISSION DATE (#45-2)</t>
-  </si>
-  <si>
-    <t>Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
-  </si>
-  <si>
     <t>Encounter.period.end</t>
   </si>
   <si>
@@ -1220,13 +1220,13 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>446: source value from PTF - DISCHARGE DATE (#45-70)</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
-  </si>
-  <si>
-    <t>446: source value from PTF - DISCHARGE DATE (#45-70)</t>
   </si>
   <si>
     <t>Encounter.length</t>
@@ -1273,6 +1273,12 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
+    <t>450: source value from PTF - PROCEDURE [#] (#45-45.01)</t>
+  </si>
+  <si>
+    <t>Inpat.InpatientDiagnosis.ICDIEN</t>
+  </si>
+  <si>
     <t>Event.reasonCode</t>
   </si>
   <si>
@@ -1283,12 +1289,6 @@
   </si>
   <si>
     <t>EVN-4 / PV2-3 (note: PV2-3 is nominally constrained to inpatient admissions; HL7 v2 makes no vocabulary suggestions for PV2-3; would not expect PV2 segment or PV2-3 to be in use in all implementations )</t>
-  </si>
-  <si>
-    <t>450: source value from PTF - PROCEDURE [#] (#45-45.01)</t>
-  </si>
-  <si>
-    <t>Inpat.InpatientDiagnosis.ICDIEN</t>
   </si>
   <si>
     <t>Encounter.reasonReference</t>
@@ -1339,6 +1339,9 @@
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
   </si>
   <si>
+    <t>1723: reference</t>
+  </si>
+  <si>
     <t>Event.reasonReference</t>
   </si>
   <si>
@@ -1346,9 +1349,6 @@
   </si>
   <si>
     <t>Resources that would commonly referenced at Encounter.indication would be Condition and/or Procedure. These most closely align with DG1/PRB and PR1 respectively.</t>
-  </si>
-  <si>
-    <t>1723: reference</t>
   </si>
   <si>
     <t>Encounter.diagnosis.use</t>
@@ -1592,12 +1592,6 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
     <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
@@ -1605,6 +1599,12 @@
 Dim.AdmitSource.AdmitSourceCode</t>
   </si>
   <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
     <t>Encounter.hospitalization.admitSource.coding.id</t>
   </si>
   <si>
@@ -1671,13 +1671,13 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>Encounter.hospitalization.admitSource.coding.display</t>
@@ -1894,16 +1894,16 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-discharge-disposition</t>
   </si>
   <si>
+    <t>456: source value from PTF - PLACE OF DISPOSITION (#45-75)</t>
+  </si>
+  <si>
+    <t>Inpat.Census.PlaceOfDispositionIEN,Inpat.Inpatient.PlaceOfDispositionIEN,Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
+  </si>
+  <si>
     <t>.dischargeDispositionCode</t>
   </si>
   <si>
     <t>PV1-36</t>
-  </si>
-  <si>
-    <t>456: source value from PTF - PLACE OF DISPOSITION (#45-75)</t>
-  </si>
-  <si>
-    <t>Inpat.Census.PlaceOfDispositionIEN,Inpat.Inpatient.PlaceOfDispositionIEN,Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
   </si>
   <si>
     <t>Encounter.location</t>
@@ -1943,6 +1943,12 @@
     <t>The location where the encounter takes place.</t>
   </si>
   <si>
+    <t>461: reference from PTF - FACILITY (#45-3)</t>
+  </si>
+  <si>
+    <t>Inpat.Census.DischargeFacility,Inpat.Inpatient.DischargeFromFacility,Inpat.InpatientFeeBasis.DischargeFacility</t>
+  </si>
+  <si>
     <t>Event.location</t>
   </si>
   <si>
@@ -1950,12 +1956,6 @@
   </si>
   <si>
     <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
-  </si>
-  <si>
-    <t>461: reference from PTF - FACILITY (#45-3)</t>
-  </si>
-  <si>
-    <t>Inpat.Census.DischargeFacility,Inpat.Inpatient.DischargeFromFacility,Inpat.InpatientFeeBasis.DischargeFacility</t>
   </si>
   <si>
     <t>Encounter.location.status</t>
@@ -2020,13 +2020,13 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
+    <t>1600: reference from PTF - FACILITY (#45-3)</t>
+  </si>
+  <si>
     <t>.particiaption[typeCode=PFM].role</t>
   </si>
   <si>
     <t>PL.6  &amp; PL.1</t>
-  </si>
-  <si>
-    <t>1600: reference from PTF - FACILITY (#45-3)</t>
   </si>
   <si>
     <t>Encounter.partOf</t>
@@ -2405,12 +2405,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="110.4140625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="110.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="191.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2643,16 +2643,16 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>82</v>
@@ -3244,13 +3244,13 @@
         <v>82</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3364,13 +3364,13 @@
         <v>82</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3484,13 +3484,13 @@
         <v>82</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3606,13 +3606,13 @@
         <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3721,22 +3721,22 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3842,13 +3842,13 @@
         <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3962,13 +3962,13 @@
         <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -4084,19 +4084,19 @@
         <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -4206,19 +4206,19 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4328,19 +4328,19 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4445,19 +4445,19 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>206</v>
@@ -4566,19 +4566,19 @@
         <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4686,19 +4686,19 @@
         <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -4926,13 +4926,13 @@
         <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5044,13 +5044,13 @@
         <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5164,13 +5164,13 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5286,13 +5286,13 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5404,13 +5404,13 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5522,13 +5522,13 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5637,22 +5637,22 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5758,13 +5758,13 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5876,13 +5876,13 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5996,13 +5996,13 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6118,13 +6118,13 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6236,13 +6236,13 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6354,13 +6354,13 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6477,13 +6477,13 @@
         <v>280</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>283</v>
@@ -6589,22 +6589,22 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6710,19 +6710,19 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6945,22 +6945,22 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -7063,16 +7063,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7181,22 +7181,22 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7302,13 +7302,13 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7422,13 +7422,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7544,13 +7544,13 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7661,22 +7661,22 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7782,19 +7782,19 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7900,19 +7900,19 @@
         <v>350</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8015,22 +8015,22 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8135,22 +8135,22 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8256,13 +8256,13 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8376,13 +8376,13 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8493,19 +8493,19 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>381</v>
@@ -8615,10 +8615,10 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>388</v>
+        <v>229</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
@@ -8627,10 +8627,10 @@
         <v>389</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8735,22 +8735,22 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8975,10 +8975,10 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>407</v>
@@ -8987,10 +8987,10 @@
         <v>408</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -9096,13 +9096,13 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9214,13 +9214,13 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9334,13 +9334,13 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9456,13 +9456,13 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9576,19 +9576,19 @@
         <v>426</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>428</v>
       </c>
       <c r="AO60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -9694,13 +9694,13 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9812,13 +9812,13 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9932,13 +9932,13 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10052,13 +10052,13 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10170,13 +10170,13 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10290,13 +10290,13 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10412,13 +10412,13 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10530,19 +10530,19 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10648,13 +10648,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10766,13 +10766,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10886,13 +10886,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11006,13 +11006,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11126,13 +11126,13 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11246,13 +11246,13 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11363,22 +11363,22 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO75" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11484,19 +11484,19 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -11602,13 +11602,13 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11722,13 +11722,13 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11839,19 +11839,19 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>510</v>
@@ -11960,13 +11960,13 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12080,13 +12080,13 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12202,19 +12202,19 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AM82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -12322,19 +12322,19 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -12439,10 +12439,10 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>533</v>
+        <v>508</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
@@ -12451,10 +12451,10 @@
         <v>534</v>
       </c>
       <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="85" hidden="true">
@@ -12562,19 +12562,19 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -12684,19 +12684,19 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AM86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="87" hidden="true">
@@ -12806,19 +12806,19 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AM87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN87" t="s" s="2">
+      <c r="AO87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="88" hidden="true">
@@ -12924,19 +12924,19 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -13046,19 +13046,19 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AM89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -13164,19 +13164,19 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="91" hidden="true">
@@ -13282,19 +13282,19 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP91" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -13400,19 +13400,19 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AM92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="93" hidden="true">
@@ -13518,13 +13518,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13638,13 +13638,13 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13758,13 +13758,13 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13878,13 +13878,13 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13998,13 +13998,13 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14115,22 +14115,22 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO98" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" hidden="true">
@@ -14233,19 +14233,19 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>610</v>
@@ -14356,13 +14356,13 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14474,13 +14474,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14594,13 +14594,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14716,13 +14716,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14834,13 +14834,13 @@
         <v>623</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>351</v>
+        <v>624</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>625</v>
+        <v>352</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>626</v>
@@ -14954,13 +14954,13 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15192,13 +15192,13 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15307,22 +15307,22 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>350</v>
+        <v>648</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>648</v>
+        <v>624</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>649</v>
       </c>
       <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="109" hidden="true">
@@ -15427,16 +15427,16 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="AL109" t="s" s="2">
+      <c r="AN109" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="659">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1082,6 +1082,9 @@
   </si>
   <si>
     <t>The period of time that the specified participant participated in the encounter. These can overlap or be sub-sets of the overall encounter's period.</t>
+  </si>
+  <si>
+    <t>1800: target not supported</t>
   </si>
   <si>
     <t>.time</t>
@@ -7779,7 +7782,7 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7788,21 +7791,21 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7825,13 +7828,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7882,7 +7885,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7897,30 +7900,30 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7943,13 +7946,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8000,7 +8003,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8024,21 +8027,21 @@
         <v>322</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8064,13 +8067,13 @@
         <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8120,7 +8123,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8141,24 +8144,24 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8273,10 +8276,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8393,10 +8396,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8419,16 +8422,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8478,7 +8481,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8487,36 +8490,36 @@
         <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8539,23 +8542,23 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>82</v>
@@ -8600,7 +8603,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8609,13 +8612,13 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>229</v>
@@ -8624,21 +8627,21 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8661,16 +8664,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8720,7 +8723,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8741,28 +8744,28 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8784,13 +8787,13 @@
         <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8819,10 +8822,10 @@
         <v>114</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8840,7 +8843,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8855,34 +8858,34 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8901,16 +8904,16 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8960,7 +8963,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8981,24 +8984,24 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9024,10 +9027,10 @@
         <v>235</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9078,7 +9081,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9102,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9113,10 +9116,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9231,10 +9234,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9351,10 +9354,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9473,14 +9476,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9499,16 +9502,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9558,7 +9561,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -9573,30 +9576,30 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9622,10 +9625,10 @@
         <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9655,10 +9658,10 @@
         <v>114</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9676,7 +9679,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9711,10 +9714,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9737,13 +9740,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9794,7 +9797,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9818,7 +9821,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9829,10 +9832,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9855,16 +9858,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9914,7 +9917,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9938,7 +9941,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9949,10 +9952,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9978,13 +9981,13 @@
         <v>235</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10034,7 +10037,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10058,7 +10061,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10069,10 +10072,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10187,10 +10190,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10307,10 +10310,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10429,10 +10432,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10458,10 +10461,10 @@
         <v>148</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10512,7 +10515,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10542,15 +10545,15 @@
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10573,13 +10576,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10630,7 +10633,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10654,7 +10657,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10665,10 +10668,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10783,10 +10786,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10903,10 +10906,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10932,13 +10935,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10988,7 +10991,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10997,7 +11000,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11023,10 +11026,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11052,13 +11055,13 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11087,10 +11090,10 @@
         <v>183</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11108,7 +11111,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11143,10 +11146,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11172,13 +11175,13 @@
         <v>148</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11228,7 +11231,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11252,7 +11255,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11263,10 +11266,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11292,13 +11295,13 @@
         <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11348,7 +11351,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11363,10 +11366,10 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
@@ -11383,10 +11386,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11412,10 +11415,10 @@
         <v>178</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11445,10 +11448,10 @@
         <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11466,7 +11469,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11490,21 +11493,21 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11619,10 +11622,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11739,10 +11742,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11768,16 +11771,16 @@
         <v>251</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11806,7 +11809,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11824,7 +11827,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11839,30 +11842,30 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11977,10 +11980,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12097,10 +12100,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12126,16 +12129,16 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12184,7 +12187,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12208,21 +12211,21 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12248,13 +12251,13 @@
         <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12304,7 +12307,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12328,21 +12331,21 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12368,14 +12371,14 @@
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12424,7 +12427,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12439,30 +12442,30 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12488,14 +12491,14 @@
         <v>156</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12544,7 +12547,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12568,21 +12571,21 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12605,19 +12608,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12666,7 +12669,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12690,21 +12693,21 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12730,16 +12733,16 @@
         <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12788,7 +12791,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12812,21 +12815,21 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12852,10 +12855,10 @@
         <v>178</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12885,10 +12888,10 @@
         <v>287</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12906,7 +12909,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12936,15 +12939,15 @@
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12970,16 +12973,16 @@
         <v>178</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13007,10 +13010,10 @@
         <v>287</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13028,7 +13031,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13052,21 +13055,21 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13092,10 +13095,10 @@
         <v>178</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13125,10 +13128,10 @@
         <v>114</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13146,7 +13149,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13170,21 +13173,21 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13210,10 +13213,10 @@
         <v>178</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13243,10 +13246,10 @@
         <v>114</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13264,7 +13267,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13288,21 +13291,21 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13325,13 +13328,13 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13382,7 +13385,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13406,21 +13409,21 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13535,10 +13538,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13655,10 +13658,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13684,13 +13687,13 @@
         <v>156</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13740,7 +13743,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13749,7 +13752,7 @@
         <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
@@ -13775,10 +13778,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13804,13 +13807,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13839,10 +13842,10 @@
         <v>183</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13860,7 +13863,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13895,10 +13898,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13924,13 +13927,13 @@
         <v>148</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13980,7 +13983,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14004,7 +14007,7 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14015,10 +14018,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14044,13 +14047,13 @@
         <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14100,7 +14103,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14115,10 +14118,10 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
@@ -14135,10 +14138,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14164,10 +14167,10 @@
         <v>178</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14197,10 +14200,10 @@
         <v>114</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14218,7 +14221,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14233,30 +14236,30 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14282,13 +14285,13 @@
         <v>235</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14338,7 +14341,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14362,7 +14365,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14373,10 +14376,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14491,10 +14494,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14611,10 +14614,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14733,10 +14736,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14759,13 +14762,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14816,7 +14819,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>90</v>
@@ -14831,30 +14834,30 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14880,13 +14883,13 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14915,10 +14918,10 @@
         <v>172</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14936,7 +14939,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14960,7 +14963,7 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14971,10 +14974,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15000,13 +15003,13 @@
         <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15035,10 +15038,10 @@
         <v>287</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15056,7 +15059,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15091,10 +15094,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15120,10 +15123,10 @@
         <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15174,7 +15177,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15198,7 +15201,7 @@
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15209,10 +15212,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15235,13 +15238,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15292,7 +15295,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15307,30 +15310,30 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15353,16 +15356,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15412,7 +15415,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15433,10 +15436,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$120</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4575" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PTF (#45) to us-core-encounter</t>
+    <t>This StructureDefinition contains the maps for VistA file PTF (45) to us-core-encounter</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -647,7 +647,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>428: source value from PTF - INTERNAL ADMISSION # (#45-2.1)</t>
+    <t>428: source value from PTF - INTERNAL ADMISSION # (45-2.1)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitEligibilityIEN,Inpat.Inpatient.AdmitEligibilityIEN,Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
@@ -724,7 +724,7 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
   </si>
   <si>
-    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (#45-70) case not null</t>
+    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) case not null</t>
   </si>
   <si>
     <t>Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
@@ -884,7 +884,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-encounter-type</t>
   </si>
   <si>
-    <t>1616: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT (#46-.01 &gt; 81-)</t>
+    <t>1616: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT (46-.01 &gt; 81-)</t>
   </si>
   <si>
     <t>Inpat.InpatientCPTProcedure.CPTIEN</t>
@@ -961,7 +961,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>441: source value from PTF - PATIENT (#45-.01)</t>
+    <t>441: reference from PTF - PATIENT (45-.01)</t>
   </si>
   <si>
     <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census535.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
@@ -1106,7 +1106,7 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
-    <t>442: reference from PTF - PROVIDER (#45-79.1)</t>
+    <t>442: reference from PTF - PROVIDER (45-79.1)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1193,7 +1193,7 @@
 </t>
   </si>
   <si>
-    <t>445: source value from PTF - ADMISSION DATE (#45-2)</t>
+    <t>445: source value from PTF - ADMISSION DATE (45-2)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
@@ -1223,7 +1223,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>446: source value from PTF - DISCHARGE DATE (#45-70)</t>
+    <t>446: source value from PTF - DISCHARGE DATE (45-70)</t>
   </si>
   <si>
     <t>./high</t>
@@ -1276,7 +1276,7 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
-    <t>450: source value from PTF - PROCEDURE [#] (#45-45.01)</t>
+    <t>450: source value from PTF - PROCEDURE [#] (45-45.01)</t>
   </si>
   <si>
     <t>Inpat.InpatientDiagnosis.ICDIEN</t>
@@ -1541,7 +1541,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>454: source value from PTF - TRANSFERRING FACILITY (#45-21.1)</t>
+    <t>454: source value from PTF - TRANSFERRING FACILITY (45-21.1)</t>
   </si>
   <si>
     <t>Inpat.Census.TransferringFacility,Inpat.Inpatient.TransferFromFacility,Inpat.InpatientFeeBasis.TransferringFacility</t>
@@ -1595,7 +1595,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
+    <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitSourceIEN,Inpat.Inpatient.AdmitSourceIEN,Inpat.InpatientFeeBasis.AdmitSourceIEN
@@ -1674,7 +1674,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
+    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; PRF CODE (45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>./code</t>
@@ -1876,7 +1876,7 @@
     <t>Encounter.hospitalization.destination.display</t>
   </si>
   <si>
-    <t>455: source value from PTF - RECEIVING FACILITY (#45-76.1)</t>
+    <t>455: source value from PTF - RECEIVING FACILITY (45-76.1)</t>
   </si>
   <si>
     <t>Inpat.Census.ReceivingFacility,Inpat.Inpatient.TransferToFacility,Inpat.InpatientFeeBasis.ReceivingFacility</t>
@@ -1897,16 +1897,49 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-discharge-disposition</t>
   </si>
   <si>
-    <t>456: source value from PTF - PLACE OF DISPOSITION (#45-75)</t>
+    <t>.dischargeDispositionCode</t>
+  </si>
+  <si>
+    <t>PV1-36</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.system</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.code</t>
+  </si>
+  <si>
+    <t>456: source value from PTF - PLACE OF DISPOSITION (45-75)</t>
   </si>
   <si>
     <t>Inpat.Census.PlaceOfDispositionIEN,Inpat.Inpatient.PlaceOfDispositionIEN,Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
   </si>
   <si>
-    <t>.dischargeDispositionCode</t>
-  </si>
-  <si>
-    <t>PV1-36</t>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.hospitalization.dischargeDisposition.text</t>
   </si>
   <si>
     <t>Encounter.location</t>
@@ -1946,7 +1979,7 @@
     <t>The location where the encounter takes place.</t>
   </si>
   <si>
-    <t>461: reference from PTF - FACILITY (#45-3)</t>
+    <t>461: reference from PTF - FACILITY (45-3)</t>
   </si>
   <si>
     <t>Inpat.Census.DischargeFacility,Inpat.Inpatient.DischargeFromFacility,Inpat.InpatientFeeBasis.DischargeFacility</t>
@@ -2023,7 +2056,7 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>1600: reference from PTF - FACILITY (#45-3)</t>
+    <t>1600: reference from PTF - FACILITY (45-3)</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -2370,11 +2403,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP109"/>
+  <dimension ref="A1:AP120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.83203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.83203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="63.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="63.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2408,7 +2441,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="110.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="108.875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
@@ -14236,30 +14269,30 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AL99" t="s" s="2">
+      <c r="AO99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP99" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>611</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14270,10 +14303,10 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
@@ -14282,17 +14315,15 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>613</v>
+        <v>157</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14341,19 +14372,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>612</v>
+        <v>159</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14365,7 +14396,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>616</v>
+        <v>160</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14376,21 +14407,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14402,15 +14433,17 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14447,31 +14480,31 @@
         <v>82</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14494,14 +14527,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14517,21 +14550,23 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>137</v>
+        <v>502</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>162</v>
+        <v>503</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14579,7 +14614,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>166</v>
+        <v>507</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14591,7 +14626,7 @@
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14603,57 +14638,53 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>160</v>
+        <v>510</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14701,19 +14732,19 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14725,7 +14756,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14736,24 +14767,24 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -14762,15 +14793,17 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>621</v>
+        <v>136</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>622</v>
+        <v>137</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14807,57 +14840,57 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>620</v>
+        <v>166</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>353</v>
+        <v>160</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14877,21 +14910,23 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>630</v>
+        <v>515</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>631</v>
+        <v>516</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14915,13 +14950,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14939,7 +14974,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>629</v>
+        <v>519</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14963,21 +14998,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>635</v>
+        <v>520</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14997,19 +15032,19 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>637</v>
+        <v>523</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>638</v>
+        <v>524</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>639</v>
+        <v>525</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15035,13 +15070,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>640</v>
+        <v>82</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15059,7 +15094,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>636</v>
+        <v>526</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15083,21 +15118,21 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>642</v>
+        <v>617</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>642</v>
+        <v>617</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15111,25 +15146,27 @@
         <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>643</v>
+        <v>530</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>644</v>
+        <v>531</v>
       </c>
       <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15177,7 +15214,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>642</v>
+        <v>533</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15192,30 +15229,30 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>345</v>
+        <v>535</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15229,25 +15266,27 @@
         <v>90</v>
       </c>
       <c r="H108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K108" t="s" s="2">
-        <v>646</v>
+        <v>156</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>647</v>
+        <v>538</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>648</v>
+        <v>539</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15295,7 +15334,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>645</v>
+        <v>541</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15310,30 +15349,30 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>649</v>
+        <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>650</v>
+        <v>542</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>651</v>
+        <v>543</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>652</v>
+        <v>621</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>652</v>
+        <v>621</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15353,21 +15392,23 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>653</v>
+        <v>545</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>654</v>
+        <v>546</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>655</v>
+        <v>547</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15415,7 +15456,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>652</v>
+        <v>550</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15436,20 +15477,1336 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K119" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AN109" t="s" s="2">
+      <c r="L119" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
+      <c r="M119" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP120" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP109">
+  <autoFilter ref="A1:AP120">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15459,7 +16816,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI108">
+  <conditionalFormatting sqref="A2:AI119">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1595,7 +1595,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (45-20 &gt; 45.1-.01)</t>
+    <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitSourceIEN,Inpat.Inpatient.AdmitSourceIEN,Inpat.InpatientFeeBasis.AdmitSourceIEN
@@ -1674,7 +1674,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; PRF CODE (45-20 &gt; 45.1-.01)</t>
+    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>./code</t>
@@ -2441,7 +2441,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="108.875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="132.34375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$131</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4575" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4995" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,9 +650,6 @@
     <t>428: source value from PTF - INTERNAL ADMISSION # (45-2.1)</t>
   </si>
   <si>
-    <t>Inpat.Census.AdmitEligibilityIEN,Inpat.Inpatient.AdmitEligibilityIEN,Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
-  </si>
-  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
@@ -727,7 +724,7 @@
     <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) case not null</t>
   </si>
   <si>
-    <t>Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
+    <t>Inpat.Census.CensusDateSID,Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -964,7 +961,7 @@
     <t>441: reference from PTF - PATIENT (45-.01)</t>
   </si>
   <si>
-    <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census535.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
+    <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census501.PatientSID,Inpat.Census535.PatientIEN,Inpat.CensusDiagnosis.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientFeeDiagnosis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1196,7 +1193,7 @@
     <t>445: source value from PTF - ADMISSION DATE (45-2)</t>
   </si>
   <si>
-    <t>Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
+    <t>Inpat.Census.AdmitDateSID,Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
   </si>
   <si>
     <t>./low</t>
@@ -1276,22 +1273,197 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>.reasonCode</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>EVN-4 / PV2-3 (note: PV2-3 is nominally constrained to inpatient admissions; HL7 v2 makes no vocabulary suggestions for PV2-3; would not expect PV2 segment or PV2-3 to be in use in all implementations )</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
     <t>450: source value from PTF - PROCEDURE [#] (45-45.01)</t>
   </si>
   <si>
-    <t>Inpat.InpatientDiagnosis.ICDIEN</t>
-  </si>
-  <si>
-    <t>Event.reasonCode</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>EVN-4 / PV2-3 (note: PV2-3 is nominally constrained to inpatient admissions; HL7 v2 makes no vocabulary suggestions for PV2-3; would not expect PV2 segment or PV2-3 to be in use in all implementations )</t>
+    <t>Inpat.CensusDiagnosis.ICDIEN,Inpat.InpatientDiagnosis.ICDIEN</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Encounter.reasonReference</t>
@@ -1577,22 +1749,7 @@
     <t>Encounter.hospitalization.admitSource.coding</t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFSourceOfAdmission</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
   </si>
   <si>
     <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
@@ -1602,12 +1759,6 @@
 Dim.AdmitSource.AdmitSourceCode</t>
   </si>
   <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.coding.id</t>
   </si>
   <si>
@@ -1617,143 +1768,22 @@
     <t>Encounter.hospitalization.admitSource.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
     <t>453: source value from PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.coding.userSelected</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Encounter.hospitalization.reAdmission</t>
@@ -2403,7 +2433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP120"/>
+  <dimension ref="A1:AP131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.30078125" customWidth="true" bestFit="true"/>
@@ -4484,27 +4514,27 @@
         <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4527,13 +4557,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4584,7 +4614,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4608,21 +4638,21 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4645,16 +4675,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4704,7 +4734,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4728,21 +4758,21 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4768,13 +4798,13 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4803,11 +4833,11 @@
         <v>172</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4824,7 +4854,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>90</v>
@@ -4839,30 +4869,30 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4885,16 +4915,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4944,7 +4974,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4979,10 +5009,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5097,10 +5127,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5217,14 +5247,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5246,10 +5276,10 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>139</v>
@@ -5304,7 +5334,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5339,10 +5369,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5368,10 +5398,10 @@
         <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5401,11 +5431,11 @@
         <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5422,7 +5452,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -5457,10 +5487,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5483,13 +5513,13 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5540,7 +5570,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5575,10 +5605,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5601,13 +5631,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5619,7 +5649,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5637,11 +5667,11 @@
         <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5658,7 +5688,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5673,30 +5703,30 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5719,13 +5749,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5776,7 +5806,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5811,10 +5841,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5929,10 +5959,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6049,14 +6079,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6078,10 +6108,10 @@
         <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -6136,7 +6166,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6171,10 +6201,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6197,13 +6227,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6233,11 +6263,11 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6254,7 +6284,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6289,10 +6319,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6315,13 +6345,13 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6372,7 +6402,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6407,10 +6437,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6436,13 +6466,13 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6471,11 +6501,11 @@
         <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6492,7 +6522,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6507,30 +6537,30 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6556,10 +6586,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6586,14 +6616,14 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Y35" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6610,7 +6640,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6631,7 +6661,7 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>160</v>
@@ -6640,15 +6670,15 @@
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6674,10 +6704,10 @@
         <v>178</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6704,14 +6734,14 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6728,7 +6758,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6752,25 +6782,25 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6789,16 +6819,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6848,7 +6878,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6863,30 +6893,30 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>309</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6909,13 +6939,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6966,7 +6996,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6987,28 +7017,28 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AO38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7027,13 +7057,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7084,7 +7114,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7105,10 +7135,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7119,10 +7149,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7145,13 +7175,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7202,7 +7232,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7223,24 +7253,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7355,10 +7385,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7475,14 +7505,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7504,10 +7534,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -7562,7 +7592,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7597,10 +7627,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7626,13 +7656,13 @@
         <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7661,10 +7691,10 @@
         <v>183</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7682,7 +7712,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7703,24 +7733,24 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7743,13 +7773,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7800,7 +7830,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7815,30 +7845,30 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>346</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7861,13 +7891,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7918,7 +7948,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7933,30 +7963,30 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7979,13 +8009,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8036,7 +8066,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8057,24 +8087,24 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8097,16 +8127,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8156,7 +8186,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8177,24 +8207,24 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8309,10 +8339,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8429,10 +8459,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8455,16 +8485,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8514,45 +8544,45 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI51" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8575,69 +8605,69 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="R52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8645,36 +8675,36 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8697,16 +8727,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8756,7 +8786,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8777,28 +8807,28 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>398</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8820,13 +8850,13 @@
         <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8855,11 +8885,11 @@
         <v>114</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>405</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8876,7 +8906,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8891,63 +8921,61 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>411</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>413</v>
+        <v>156</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>157</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8996,19 +9024,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>159</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -9017,28 +9045,28 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>409</v>
+        <v>160</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9054,18 +9082,20 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>137</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9102,19 +9132,19 @@
         <v>82</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>415</v>
+        <v>166</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9126,7 +9156,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -9138,7 +9168,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>418</v>
+        <v>160</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9149,10 +9179,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9163,7 +9193,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9172,19 +9202,23 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>157</v>
+        <v>412</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9232,19 +9266,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>159</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9256,32 +9290,32 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>160</v>
+        <v>417</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9293,17 +9327,15 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9352,19 +9384,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9387,14 +9419,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9407,26 +9439,24 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>243</v>
+        <v>137</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O59" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9462,19 +9492,19 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>245</v>
+        <v>166</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9498,7 +9528,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9509,24 +9539,24 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9535,18 +9565,20 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9594,10 +9626,10 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>90</v>
@@ -9609,30 +9641,30 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9652,18 +9684,20 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9688,13 +9722,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9712,7 +9746,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9736,13 +9770,13 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>160</v>
+        <v>434</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
     </row>
     <row r="62" hidden="true">
@@ -9764,25 +9798,27 @@
         <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9830,7 +9866,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9845,30 +9881,30 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9879,7 +9915,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9888,21 +9924,21 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>442</v>
+        <v>156</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9950,13 +9986,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9974,21 +10010,21 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10002,27 +10038,29 @@
         <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>235</v>
+        <v>453</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10070,7 +10108,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10094,21 +10132,21 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10128,19 +10166,23 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>156</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>157</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10188,7 +10230,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>159</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10200,7 +10242,7 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10212,25 +10254,25 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>160</v>
+        <v>467</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>135</v>
+        <v>399</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10240,25 +10282,25 @@
         <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>470</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>137</v>
+        <v>471</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>162</v>
+        <v>401</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10308,7 +10350,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>166</v>
+        <v>469</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10320,7 +10362,7 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10329,28 +10371,28 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10363,26 +10405,22 @@
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>234</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>243</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10430,7 +10468,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>245</v>
+        <v>472</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10442,7 +10480,7 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10454,7 +10492,7 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>133</v>
+        <v>475</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10465,10 +10503,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10491,13 +10529,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>456</v>
+        <v>157</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>457</v>
+        <v>158</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10548,7 +10586,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>159</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10560,7 +10598,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10572,32 +10610,32 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10609,15 +10647,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>460</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>461</v>
+        <v>137</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10666,19 +10706,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>459</v>
+        <v>166</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10690,7 +10730,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>463</v>
+        <v>160</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10701,42 +10741,46 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>157</v>
+        <v>242</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10784,19 +10828,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>159</v>
+        <v>244</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10808,7 +10852,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10819,42 +10863,42 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>135</v>
+        <v>480</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>136</v>
+        <v>481</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>137</v>
+        <v>482</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>162</v>
+        <v>483</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10892,57 +10936,57 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>166</v>
+        <v>479</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>160</v>
+        <v>486</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10962,20 +11006,18 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11000,13 +11042,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11024,7 +11066,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11033,7 +11075,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11048,7 +11090,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11059,10 +11101,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11082,20 +11124,18 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>104</v>
+        <v>494</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11120,13 +11160,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11144,7 +11184,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11168,7 +11208,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>133</v>
+        <v>497</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11179,10 +11219,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11193,7 +11233,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11202,19 +11242,19 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>148</v>
+        <v>499</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11264,13 +11304,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11288,7 +11328,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11299,10 +11339,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11322,19 +11362,19 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11384,7 +11424,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11399,16 +11439,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>133</v>
+        <v>508</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11419,10 +11459,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11445,13 +11485,13 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>493</v>
+        <v>157</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>494</v>
+        <v>158</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11478,13 +11518,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11502,7 +11542,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>492</v>
+        <v>159</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11514,7 +11554,7 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11526,32 +11566,32 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>497</v>
+        <v>160</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11563,15 +11603,17 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11620,19 +11662,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11655,14 +11697,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11675,24 +11717,26 @@
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11728,19 +11772,19 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11764,7 +11808,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11775,10 +11819,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11789,32 +11833,28 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11838,11 +11878,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11860,13 +11902,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11875,30 +11917,30 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>510</v>
+        <v>152</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11921,13 +11963,13 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>156</v>
+        <v>517</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>157</v>
+        <v>518</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>158</v>
+        <v>519</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11978,7 +12020,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>159</v>
+        <v>516</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11990,7 +12032,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12002,7 +12044,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>160</v>
+        <v>520</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12013,21 +12055,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12039,17 +12081,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12086,31 +12126,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12133,21 +12173,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12156,23 +12196,21 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>515</v>
+        <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>516</v>
+        <v>162</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12208,31 +12246,31 @@
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>519</v>
+        <v>166</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12244,21 +12282,21 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>520</v>
+        <v>160</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12284,13 +12322,13 @@
         <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12340,7 +12378,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12349,7 +12387,7 @@
         <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>102</v>
@@ -12364,13 +12402,13 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>527</v>
+        <v>133</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -12392,7 +12430,7 @@
         <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12401,7 +12439,7 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>530</v>
@@ -12409,10 +12447,10 @@
       <c r="M84" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>532</v>
       </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12436,13 +12474,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12460,7 +12498,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12475,30 +12513,30 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>535</v>
+        <v>133</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12521,18 +12559,18 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12580,7 +12618,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12604,21 +12642,21 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12632,7 +12670,7 @@
         <v>90</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
@@ -12641,20 +12679,18 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L86" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>549</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12702,7 +12738,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12717,30 +12753,30 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>551</v>
+        <v>133</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12760,23 +12796,19 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12800,13 +12832,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12824,7 +12856,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12848,21 +12880,21 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12885,13 +12917,13 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>562</v>
+        <v>157</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>563</v>
+        <v>158</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12918,13 +12950,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12942,7 +12974,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>159</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12954,7 +12986,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12972,19 +13004,19 @@
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13003,20 +13035,18 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>568</v>
+        <v>137</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>569</v>
+        <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13040,31 +13070,31 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>567</v>
+        <v>166</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13076,7 +13106,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13088,21 +13118,21 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>574</v>
+        <v>160</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13116,25 +13146,29 @@
         <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>577</v>
+        <v>412</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13158,13 +13192,11 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13182,7 +13214,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>576</v>
+        <v>416</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13197,30 +13229,30 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>581</v>
+        <v>417</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>582</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13231,7 +13263,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13243,13 +13275,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>157</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13276,13 +13308,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13300,19 +13332,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>583</v>
+        <v>159</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13324,32 +13356,32 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>588</v>
+        <v>160</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13361,15 +13393,17 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>460</v>
+        <v>136</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>137</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13406,31 +13440,31 @@
         <v>82</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>590</v>
+        <v>166</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13442,21 +13476,21 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>593</v>
+        <v>160</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13476,19 +13510,23 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>157</v>
+        <v>422</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13536,7 +13574,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>159</v>
+        <v>426</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13548,7 +13586,7 @@
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13560,32 +13598,32 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>160</v>
+        <v>427</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13594,19 +13632,19 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>137</v>
+        <v>430</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>139</v>
+        <v>432</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13644,31 +13682,31 @@
         <v>82</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>166</v>
+        <v>433</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13680,21 +13718,21 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>160</v>
+        <v>434</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13708,7 +13746,7 @@
         <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13717,18 +13755,18 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13776,7 +13814,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13785,36 +13823,36 @@
         <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>82</v>
+        <v>567</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>133</v>
+        <v>443</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13837,18 +13875,18 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13872,13 +13910,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13896,7 +13934,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13920,21 +13958,21 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>133</v>
+        <v>450</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13957,18 +13995,20 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>148</v>
+        <v>453</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14016,7 +14056,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14040,21 +14080,21 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14068,7 +14108,7 @@
         <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
@@ -14080,15 +14120,17 @@
         <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14136,7 +14178,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14151,30 +14193,30 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>133</v>
+        <v>467</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14188,7 +14230,7 @@
         <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>82</v>
@@ -14200,10 +14242,10 @@
         <v>178</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>604</v>
+        <v>572</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>605</v>
+        <v>573</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14230,13 +14272,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>114</v>
+        <v>286</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>606</v>
+        <v>574</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14254,7 +14296,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14278,21 +14320,21 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>608</v>
+        <v>160</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>609</v>
+        <v>576</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>610</v>
+        <v>577</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>610</v>
+        <v>577</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14303,7 +14345,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14315,16 +14357,20 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>157</v>
+        <v>578</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14348,13 +14394,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14372,19 +14418,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>159</v>
+        <v>577</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14396,25 +14442,25 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>160</v>
+        <v>584</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14433,17 +14479,15 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>137</v>
+        <v>587</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14468,31 +14512,31 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>166</v>
+        <v>586</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14504,7 +14548,7 @@
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14516,21 +14560,21 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>160</v>
+        <v>591</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14550,23 +14594,19 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>251</v>
+        <v>178</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>502</v>
+        <v>594</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14590,13 +14630,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14614,7 +14654,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>507</v>
+        <v>593</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14638,21 +14678,21 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>510</v>
+        <v>598</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>511</v>
+        <v>599</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14675,13 +14715,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>156</v>
+        <v>517</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>157</v>
+        <v>601</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>158</v>
+        <v>602</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14732,7 +14772,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>159</v>
+        <v>600</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14744,7 +14784,7 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14756,32 +14796,32 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>160</v>
+        <v>603</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14793,17 +14833,15 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14840,31 +14878,31 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -14887,21 +14925,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14910,23 +14948,21 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>515</v>
+        <v>137</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>516</v>
+        <v>162</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14962,31 +14998,31 @@
         <v>82</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>519</v>
+        <v>166</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -14998,21 +15034,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>520</v>
+        <v>160</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15038,13 +15074,13 @@
         <v>156</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15094,7 +15130,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15103,7 +15139,7 @@
         <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>102</v>
@@ -15118,21 +15154,21 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>527</v>
+        <v>133</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15146,7 +15182,7 @@
         <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
@@ -15155,7 +15191,7 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>530</v>
@@ -15163,10 +15199,10 @@
       <c r="M107" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>532</v>
       </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15190,13 +15226,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15214,7 +15250,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15229,30 +15265,30 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>535</v>
+        <v>133</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15275,18 +15311,18 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N108" s="2"/>
-      <c r="O108" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15334,7 +15370,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15358,21 +15394,21 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15386,7 +15422,7 @@
         <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
@@ -15395,20 +15431,18 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L109" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>549</v>
-      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15456,7 +15490,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15471,30 +15505,30 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>551</v>
+        <v>133</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15508,29 +15542,25 @@
         <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15554,13 +15584,13 @@
         <v>82</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15578,7 +15608,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>558</v>
+        <v>613</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15602,21 +15632,21 @@
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>559</v>
+        <v>618</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>560</v>
+        <v>619</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15627,10 +15657,10 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
@@ -15639,17 +15669,15 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>624</v>
+        <v>157</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15698,19 +15726,19 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>623</v>
+        <v>159</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15722,7 +15750,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>627</v>
+        <v>160</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15733,21 +15761,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
@@ -15759,15 +15787,17 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15804,31 +15834,31 @@
         <v>82</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -15851,14 +15881,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15874,21 +15904,23 @@
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>137</v>
+        <v>412</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>162</v>
+        <v>413</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -15936,7 +15968,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>166</v>
+        <v>416</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -15948,7 +15980,7 @@
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -15960,57 +15992,53 @@
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>160</v>
+        <v>417</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>82</v>
       </c>
@@ -16058,19 +16086,19 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>82</v>
@@ -16082,7 +16110,7 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16093,24 +16121,24 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>82</v>
@@ -16119,15 +16147,17 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>632</v>
+        <v>136</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>633</v>
+        <v>137</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16164,57 +16194,57 @@
         <v>82</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>631</v>
+        <v>166</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>353</v>
+        <v>160</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>639</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>640</v>
+        <v>625</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16234,21 +16264,23 @@
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>641</v>
+        <v>422</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>642</v>
+        <v>423</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16272,13 +16304,13 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>645</v>
+        <v>82</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16296,7 +16328,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>640</v>
+        <v>426</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16320,21 +16352,21 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>646</v>
+        <v>427</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16354,19 +16386,19 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>648</v>
+        <v>430</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>649</v>
+        <v>431</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>650</v>
+        <v>432</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16392,13 +16424,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>651</v>
+        <v>82</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16416,7 +16448,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>647</v>
+        <v>433</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16440,21 +16472,21 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16468,25 +16500,27 @@
         <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>654</v>
+        <v>437</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>655</v>
+        <v>438</v>
       </c>
       <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16534,7 +16568,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>653</v>
+        <v>440</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16549,30 +16583,30 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>345</v>
+        <v>443</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>656</v>
+        <v>630</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>656</v>
+        <v>630</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16586,25 +16620,27 @@
         <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J119" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K119" t="s" s="2">
-        <v>657</v>
+        <v>156</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>658</v>
+        <v>446</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>659</v>
+        <v>447</v>
       </c>
       <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
       </c>
@@ -16652,7 +16688,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>656</v>
+        <v>449</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16667,30 +16703,30 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>661</v>
+        <v>450</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>662</v>
+        <v>451</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16710,21 +16746,23 @@
         <v>82</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>664</v>
+        <v>453</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>665</v>
+        <v>454</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>666</v>
+        <v>455</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -16772,7 +16810,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>663</v>
+        <v>458</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16793,20 +16831,1336 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="AN120" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="AO120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP120" t="s" s="2">
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP131" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP120">
+  <autoFilter ref="A1:AP131">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16816,7 +18170,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI119">
+  <conditionalFormatting sqref="A2:AI130">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$197</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6559" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="797">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1631,49 +1631,184 @@
     <t>EVN-4 / PV2-3 (note: PV2-3 is nominally constrained to inpatient admissions; HL7 v2 makes no vocabulary suggestions for PV2-3; would not expect PV2 segment or PV2-3 to be in use in all implementations )</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle</t>
+  </si>
+  <si>
+    <t>va-principle</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-principle.id</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.id</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle.extension</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.extension</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle.coding</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle.coding.id</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding.id</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle.coding.extension</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding.extension</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle.coding.system</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding.system</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/sid/icd-10-pcs</t>
-  </si>
-  <si>
-    <t>450-1: fixed value = http://hl7.org/fhir/sid/icd-10-pcs</t>
+    <t>urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>448-1: fixed value = urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-principle.coding.version</t>
   </si>
   <si>
     <t>Encounter.reasonCode.coding.version</t>
   </si>
   <si>
+    <t>Encounter.reasonCode:va-principle.coding.code</t>
+  </si>
+  <si>
     <t>Encounter.reasonCode.coding.code</t>
   </si>
   <si>
+    <t>448: source value from PTF - PRINCIPAL DIAGNOSIS (45-79)</t>
+  </si>
+  <si>
+    <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-principle.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-principle.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-principle.text</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode.text</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary</t>
+  </si>
+  <si>
+    <t>va-secundary</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.system</t>
+  </si>
+  <si>
+    <t>449-1: fixed value = urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.code</t>
+  </si>
+  <si>
+    <t>449: source value from PTF - SECONDARY DIAGNOSIS [#] (45-79.16)</t>
+  </si>
+  <si>
+    <t>Inpat.CensusDiagnosis.ICDIEN,Inpat.InpatientDiagnosis.ICDIEN</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secundary.text</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure</t>
+  </si>
+  <si>
+    <t>va-procedure</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding.system</t>
+  </si>
+  <si>
+    <t>http://www.cms.gov/Medicare/Coding/ICD10</t>
+  </si>
+  <si>
+    <t>450-1: fixed value = http://www.cms.gov/Medicare/Coding/ICD10</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding.code</t>
+  </si>
+  <si>
     <t>450: source value from PTF - PROCEDURE [#] (45-45.01)</t>
   </si>
   <si>
-    <t>Inpat.CensusDiagnosis.ICDIEN,Inpat.InpatientDiagnosis.ICDIEN</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode.text</t>
+    <t>Encounter.reasonCode:va-procedure.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-procedure.text</t>
   </si>
   <si>
     <t>Encounter.reasonReference</t>
@@ -2655,12 +2790,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP172"/>
+  <dimension ref="A1:AP197"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="63.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.45703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -14048,16 +14183,14 @@
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>511</v>
@@ -14098,11 +14231,13 @@
         <v>522</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14112,24 +14247,26 @@
         <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>159</v>
+        <v>513</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14154,13 +14291,13 @@
         <v>82</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14178,19 +14315,19 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>511</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14199,35 +14336,35 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>162</v>
+        <v>519</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -14239,17 +14376,15 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14286,31 +14421,31 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14333,14 +14468,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14356,23 +14491,21 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>233</v>
+        <v>136</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>234</v>
+        <v>137</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>235</v>
+        <v>164</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14408,19 +14541,19 @@
         <v>82</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14432,7 +14565,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14444,21 +14577,21 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14469,7 +14602,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14478,19 +14611,23 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>158</v>
+        <v>233</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14538,19 +14675,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14562,32 +14699,32 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14599,17 +14736,15 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14646,31 +14781,31 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14693,46 +14828,44 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>346</v>
+        <v>164</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14741,7 +14874,7 @@
         <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>82</v>
@@ -14768,34 +14901,34 @@
         <v>82</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>350</v>
+        <v>167</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14804,21 +14937,21 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>352</v>
+        <v>162</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14832,7 +14965,7 @@
         <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>82</v>
@@ -14841,18 +14974,20 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14861,7 +14996,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14900,7 +15035,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14915,7 +15050,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14924,21 +15059,21 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14952,7 +15087,7 @@
         <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>82</v>
@@ -14961,18 +15096,18 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -15020,7 +15155,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15035,30 +15170,30 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15072,7 +15207,7 @@
         <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -15081,17 +15216,17 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15140,7 +15275,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15155,30 +15290,30 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15201,19 +15336,17 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>380</v>
+        <v>158</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15262,7 +15395,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15286,21 +15419,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15323,19 +15456,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>158</v>
+        <v>380</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>243</v>
+        <v>381</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>244</v>
+        <v>382</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>245</v>
+        <v>383</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>246</v>
+        <v>384</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15384,7 +15517,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>248</v>
+        <v>385</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15408,35 +15541,35 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>250</v>
+        <v>386</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>251</v>
+        <v>387</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
@@ -15445,18 +15578,20 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>538</v>
+        <v>158</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>539</v>
+        <v>243</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>514</v>
+        <v>244</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15504,13 +15639,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>537</v>
+        <v>248</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15525,38 +15660,40 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>519</v>
+        <v>250</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>521</v>
+        <v>251</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="D108" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>82</v>
@@ -15565,15 +15702,17 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>291</v>
+        <v>179</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15598,13 +15737,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15622,7 +15761,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15643,24 +15782,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15775,10 +15914,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15848,16 +15987,16 @@
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>167</v>
@@ -15895,14 +16034,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15915,25 +16054,25 @@
         <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15982,7 +16121,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15994,7 +16133,7 @@
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -16006,54 +16145,52 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>549</v>
+        <v>158</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>550</v>
+        <v>159</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16102,10 +16239,10 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>547</v>
+        <v>161</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>90</v>
@@ -16114,25 +16251,25 @@
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>554</v>
+        <v>162</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113" hidden="true">
@@ -16140,18 +16277,18 @@
         <v>556</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>556</v>
+        <v>533</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>82</v>
@@ -16163,15 +16300,17 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>557</v>
+        <v>137</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16196,43 +16335,43 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>556</v>
+        <v>167</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16255,10 +16394,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16272,25 +16411,29 @@
         <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>562</v>
+        <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>563</v>
+        <v>345</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
       </c>
@@ -16299,7 +16442,7 @@
         <v>82</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>82</v>
@@ -16338,7 +16481,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>561</v>
+        <v>350</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16353,7 +16496,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
@@ -16362,21 +16505,21 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>565</v>
+        <v>352</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>566</v>
+        <v>539</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16387,7 +16530,7 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
@@ -16396,19 +16539,19 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>567</v>
+        <v>158</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>568</v>
+        <v>355</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>569</v>
+        <v>356</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>570</v>
+        <v>357</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16458,13 +16601,13 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>566</v>
+        <v>358</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
@@ -16482,21 +16625,21 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>571</v>
+        <v>359</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>572</v>
+        <v>541</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16516,21 +16659,21 @@
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>291</v>
+        <v>110</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>573</v>
+        <v>362</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16578,7 +16721,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>572</v>
+        <v>365</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16593,30 +16736,30 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>576</v>
+        <v>368</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16636,19 +16779,21 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>159</v>
+        <v>371</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>160</v>
+        <v>372</v>
       </c>
       <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16696,7 +16841,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>161</v>
+        <v>374</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16708,7 +16853,7 @@
         <v>82</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>82</v>
@@ -16720,32 +16865,32 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>162</v>
+        <v>377</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>578</v>
+        <v>547</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>82</v>
@@ -16754,21 +16899,23 @@
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>136</v>
+        <v>380</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>137</v>
+        <v>381</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>164</v>
+        <v>382</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16816,19 +16963,19 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>167</v>
+        <v>385</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
@@ -16840,56 +16987,56 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>162</v>
+        <v>386</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J119" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16938,19 +17085,19 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>301</v>
+        <v>248</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -16962,25 +17109,27 @@
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C120" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="D120" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16990,24 +17139,26 @@
         <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>581</v>
+        <v>513</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17032,13 +17183,13 @@
         <v>82</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -17056,13 +17207,13 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>580</v>
+        <v>511</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>82</v>
@@ -17077,24 +17228,24 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>154</v>
+        <v>519</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>583</v>
+        <v>521</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>584</v>
+        <v>525</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17117,13 +17268,13 @@
         <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>585</v>
+        <v>158</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>586</v>
+        <v>159</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>587</v>
+        <v>160</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17174,7 +17325,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>584</v>
+        <v>161</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17186,7 +17337,7 @@
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
@@ -17198,7 +17349,7 @@
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>588</v>
+        <v>162</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -17209,21 +17360,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -17235,15 +17386,17 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17280,31 +17433,31 @@
         <v>82</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17327,14 +17480,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>590</v>
+        <v>529</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17350,21 +17503,23 @@
         <v>82</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O123" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
@@ -17400,19 +17555,19 @@
         <v>82</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17424,7 +17579,7 @@
         <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>82</v>
@@ -17436,21 +17591,21 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>591</v>
+        <v>531</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17470,20 +17625,18 @@
         <v>82</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>592</v>
+        <v>159</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17532,7 +17685,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>595</v>
+        <v>161</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17541,10 +17694,10 @@
         <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>82</v>
@@ -17556,7 +17709,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17567,21 +17720,21 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>597</v>
+        <v>533</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>82</v>
@@ -17590,19 +17743,19 @@
         <v>82</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>598</v>
+        <v>137</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>599</v>
+        <v>164</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>600</v>
+        <v>139</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17628,43 +17781,43 @@
         <v>82</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>603</v>
+        <v>167</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>82</v>
@@ -17676,7 +17829,7 @@
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17687,10 +17840,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>604</v>
+        <v>573</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>604</v>
+        <v>535</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17704,7 +17857,7 @@
         <v>90</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>82</v>
@@ -17713,18 +17866,20 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>605</v>
+        <v>345</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>606</v>
+        <v>346</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17733,7 +17888,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -17772,7 +17927,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>608</v>
+        <v>350</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17787,7 +17942,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -17796,21 +17951,21 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>609</v>
+        <v>352</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>610</v>
+        <v>576</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>610</v>
+        <v>539</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17824,7 +17979,7 @@
         <v>90</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>82</v>
@@ -17836,13 +17991,13 @@
         <v>158</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>611</v>
+        <v>355</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>612</v>
+        <v>356</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>613</v>
+        <v>357</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17892,7 +18047,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>614</v>
+        <v>358</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17907,30 +18062,30 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>133</v>
+        <v>359</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>617</v>
+        <v>577</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>617</v>
+        <v>541</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17944,25 +18099,27 @@
         <v>90</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>618</v>
+        <v>362</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>619</v>
+        <v>363</v>
       </c>
       <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+      <c r="O128" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -17986,13 +18143,13 @@
         <v>82</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -18010,7 +18167,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>617</v>
+        <v>365</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18025,7 +18182,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>82</v>
@@ -18034,21 +18191,21 @@
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>622</v>
+        <v>368</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>623</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>624</v>
+        <v>579</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>545</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18068,19 +18225,21 @@
         <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>159</v>
+        <v>371</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>160</v>
+        <v>372</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+      <c r="O129" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -18128,7 +18287,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>161</v>
+        <v>374</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18140,7 +18299,7 @@
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>82</v>
@@ -18152,32 +18311,32 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>162</v>
+        <v>377</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>625</v>
+        <v>580</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>625</v>
+        <v>547</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>82</v>
@@ -18186,21 +18345,23 @@
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>136</v>
+        <v>380</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>137</v>
+        <v>381</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>164</v>
+        <v>382</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -18236,31 +18397,31 @@
         <v>82</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>167</v>
+        <v>385</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
@@ -18272,21 +18433,21 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>162</v>
+        <v>386</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>626</v>
+        <v>581</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>626</v>
+        <v>549</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18297,10 +18458,10 @@
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>82</v>
@@ -18309,19 +18470,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18346,11 +18507,13 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18368,13 +18531,13 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
@@ -18383,61 +18546,63 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>630</v>
+        <v>582</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>630</v>
+        <v>582</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>158</v>
+        <v>583</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>159</v>
+        <v>584</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18486,19 +18651,19 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>161</v>
+        <v>582</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>82</v>
@@ -18507,28 +18672,28 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>162</v>
+        <v>519</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18544,20 +18709,18 @@
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>137</v>
+        <v>586</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18594,19 +18757,19 @@
         <v>82</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>167</v>
+        <v>585</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18618,7 +18781,7 @@
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
@@ -18630,7 +18793,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>162</v>
+        <v>588</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18641,10 +18804,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>632</v>
+        <v>589</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>632</v>
+        <v>589</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18658,29 +18821,25 @@
         <v>90</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>345</v>
+        <v>159</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18689,7 +18848,7 @@
         <v>82</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>82</v>
@@ -18728,7 +18887,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18740,10 +18899,10 @@
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>82</v>
@@ -18752,32 +18911,32 @@
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>352</v>
+        <v>162</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>635</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>635</v>
+        <v>590</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>82</v>
@@ -18786,19 +18945,19 @@
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>355</v>
+        <v>137</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18848,19 +19007,19 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>358</v>
+        <v>167</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>82</v>
@@ -18872,54 +19031,56 @@
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>359</v>
+        <v>162</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>636</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>636</v>
+        <v>591</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I136" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>362</v>
+        <v>299</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O136" t="s" s="2">
-        <v>364</v>
+        <v>145</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18968,59 +19129,59 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>368</v>
+        <v>133</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>638</v>
+        <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>638</v>
+        <v>592</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>82</v>
@@ -19029,18 +19190,18 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>158</v>
+        <v>594</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>371</v>
+        <v>595</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -19088,10 +19249,10 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>374</v>
+        <v>592</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>90</v>
@@ -19103,30 +19264,30 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>377</v>
+        <v>599</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>378</v>
+        <v>600</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19146,23 +19307,19 @@
         <v>82</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>380</v>
+        <v>179</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>381</v>
+        <v>602</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19186,13 +19343,13 @@
         <v>82</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -19210,7 +19367,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>385</v>
+        <v>601</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19234,21 +19391,21 @@
         <v>82</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>386</v>
+        <v>162</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>640</v>
+        <v>606</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>640</v>
+        <v>606</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19268,23 +19425,19 @@
         <v>82</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>158</v>
+        <v>607</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>243</v>
+        <v>608</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
@@ -19332,7 +19485,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>248</v>
+        <v>606</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19356,21 +19509,21 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>250</v>
+        <v>610</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19381,7 +19534,7 @@
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
@@ -19393,15 +19546,17 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>179</v>
+        <v>612</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>642</v>
+        <v>613</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19426,13 +19581,13 @@
         <v>82</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>645</v>
+        <v>82</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -19450,13 +19605,13 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
@@ -19474,21 +19629,21 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>162</v>
+        <v>616</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>646</v>
+        <v>82</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19499,10 +19654,10 @@
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>82</v>
@@ -19511,20 +19666,18 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>648</v>
+        <v>618</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>649</v>
+        <v>619</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19548,13 +19701,13 @@
         <v>82</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19572,13 +19725,13 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>82</v>
@@ -19596,21 +19749,21 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>654</v>
+        <v>621</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>656</v>
+        <v>622</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>656</v>
+        <v>622</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19621,7 +19774,7 @@
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>82</v>
@@ -19633,13 +19786,13 @@
         <v>82</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>657</v>
+        <v>159</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>658</v>
+        <v>160</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19666,13 +19819,13 @@
         <v>82</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19690,19 +19843,19 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>656</v>
+        <v>161</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>82</v>
@@ -19714,25 +19867,25 @@
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>661</v>
+        <v>162</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19751,15 +19904,17 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>664</v>
+        <v>137</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19784,13 +19939,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>666</v>
+        <v>82</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19808,7 +19963,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>663</v>
+        <v>167</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19820,7 +19975,7 @@
         <v>82</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>82</v>
@@ -19832,53 +19987,57 @@
         <v>82</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>668</v>
+        <v>162</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>670</v>
+        <v>624</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>670</v>
+        <v>624</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I144" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>585</v>
+        <v>136</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>671</v>
+        <v>299</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19926,19 +20085,19 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>670</v>
+        <v>301</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>82</v>
@@ -19950,21 +20109,21 @@
         <v>82</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>673</v>
+        <v>133</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>675</v>
+        <v>625</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>675</v>
+        <v>625</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19987,13 +20146,13 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>159</v>
+        <v>626</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>160</v>
+        <v>627</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20044,7 +20203,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>161</v>
+        <v>625</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20056,7 +20215,7 @@
         <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
@@ -20068,32 +20227,32 @@
         <v>82</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>676</v>
+        <v>629</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>676</v>
+        <v>629</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>82</v>
@@ -20105,17 +20264,15 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>136</v>
+        <v>630</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>137</v>
+        <v>631</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20152,31 +20309,31 @@
         <v>82</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>167</v>
+        <v>629</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>82</v>
@@ -20188,7 +20345,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>162</v>
+        <v>633</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20199,10 +20356,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20222,20 +20379,18 @@
         <v>82</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>592</v>
+        <v>159</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20284,7 +20439,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>595</v>
+        <v>161</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20293,10 +20448,10 @@
         <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>82</v>
@@ -20308,7 +20463,7 @@
         <v>82</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
@@ -20319,21 +20474,21 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -20342,19 +20497,19 @@
         <v>82</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>598</v>
+        <v>137</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>599</v>
+        <v>164</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>600</v>
+        <v>139</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20380,43 +20535,43 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>603</v>
+        <v>167</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>82</v>
@@ -20428,7 +20583,7 @@
         <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20439,10 +20594,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>679</v>
+        <v>636</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>679</v>
+        <v>636</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20465,16 +20620,16 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20524,7 +20679,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20533,7 +20688,7 @@
         <v>90</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>102</v>
@@ -20548,7 +20703,7 @@
         <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>609</v>
+        <v>133</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20559,10 +20714,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>680</v>
+        <v>642</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>680</v>
+        <v>642</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20576,7 +20731,7 @@
         <v>90</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>82</v>
@@ -20585,16 +20740,16 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20620,13 +20775,13 @@
         <v>82</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20644,7 +20799,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>614</v>
+        <v>648</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20659,10 +20814,10 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>681</v>
+        <v>82</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>682</v>
+        <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>82</v>
@@ -20679,10 +20834,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>683</v>
+        <v>649</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>683</v>
+        <v>649</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20696,24 +20851,26 @@
         <v>90</v>
       </c>
       <c r="H151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J151" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I151" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K151" t="s" s="2">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>684</v>
+        <v>650</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20738,13 +20895,13 @@
         <v>82</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>686</v>
+        <v>82</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>82</v>
@@ -20762,7 +20919,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>683</v>
+        <v>653</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20786,21 +20943,21 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>688</v>
+        <v>654</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>689</v>
+        <v>82</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20814,24 +20971,26 @@
         <v>90</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>159</v>
+        <v>656</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>657</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>658</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20880,7 +21039,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>161</v>
+        <v>659</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20892,19 +21051,19 @@
         <v>82</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>82</v>
@@ -20915,21 +21074,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>691</v>
+        <v>662</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>691</v>
+        <v>662</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>82</v>
@@ -20941,17 +21100,15 @@
         <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>137</v>
+        <v>663</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20976,43 +21133,43 @@
         <v>82</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>82</v>
+        <v>666</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>167</v>
+        <v>662</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>82</v>
@@ -21024,21 +21181,21 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>162</v>
+        <v>667</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>82</v>
+        <v>668</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>692</v>
+        <v>669</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>692</v>
+        <v>669</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21049,7 +21206,7 @@
         <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>82</v>
@@ -21058,23 +21215,19 @@
         <v>82</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>82</v>
       </c>
@@ -21122,19 +21275,19 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>238</v>
+        <v>161</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>82</v>
@@ -21146,32 +21299,32 @@
         <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>693</v>
+        <v>670</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>693</v>
+        <v>670</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>82</v>
@@ -21183,15 +21336,17 @@
         <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N155" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21228,31 +21383,31 @@
         <v>82</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>82</v>
@@ -21275,14 +21430,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>694</v>
+        <v>671</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>694</v>
+        <v>671</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21292,27 +21447,29 @@
         <v>81</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>137</v>
+        <v>234</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O156" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21336,31 +21493,29 @@
         <v>82</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>82</v>
+        <v>672</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21372,33 +21527,33 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>82</v>
+        <v>673</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21412,29 +21567,25 @@
         <v>90</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>345</v>
+        <v>159</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>82</v>
       </c>
@@ -21443,7 +21594,7 @@
         <v>82</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>696</v>
+        <v>82</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>82</v>
@@ -21482,7 +21633,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21494,10 +21645,10 @@
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>697</v>
+        <v>82</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>82</v>
@@ -21506,32 +21657,32 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>352</v>
+        <v>162</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>82</v>
@@ -21540,19 +21691,19 @@
         <v>82</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>355</v>
+        <v>137</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>357</v>
+        <v>139</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -21590,31 +21741,31 @@
         <v>82</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>358</v>
+        <v>167</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>82</v>
@@ -21626,21 +21777,21 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>359</v>
+        <v>162</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21663,17 +21814,19 @@
         <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N159" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O159" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -21683,7 +21836,7 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>82</v>
@@ -21722,7 +21875,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21737,30 +21890,30 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>701</v>
+        <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>369</v>
+        <v>353</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>702</v>
+        <v>680</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>702</v>
+        <v>680</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21786,15 +21939,15 @@
         <v>158</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
@@ -21842,7 +21995,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21866,21 +22019,21 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>703</v>
+        <v>681</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>703</v>
+        <v>681</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21894,7 +22047,7 @@
         <v>90</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>82</v>
@@ -21903,19 +22056,17 @@
         <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -21964,7 +22115,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21979,30 +22130,30 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>387</v>
+        <v>369</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22028,16 +22179,14 @@
         <v>158</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>243</v>
+        <v>371</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -22086,7 +22235,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>248</v>
+        <v>374</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22110,21 +22259,21 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>251</v>
+        <v>378</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22135,30 +22284,32 @@
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J163" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I163" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J163" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K163" t="s" s="2">
-        <v>291</v>
+        <v>380</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>706</v>
+        <v>381</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>707</v>
+        <v>382</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="O163" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
       </c>
@@ -22206,13 +22357,13 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>705</v>
+        <v>385</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>82</v>
@@ -22230,21 +22381,21 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>709</v>
+        <v>386</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>710</v>
+        <v>685</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>710</v>
+        <v>685</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22264,19 +22415,23 @@
         <v>82</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
       </c>
@@ -22324,7 +22479,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22336,7 +22491,7 @@
         <v>82</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>82</v>
@@ -22348,32 +22503,32 @@
         <v>82</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>711</v>
+        <v>686</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>711</v>
+        <v>686</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>82</v>
@@ -22385,17 +22540,15 @@
         <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>137</v>
+        <v>687</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22420,13 +22573,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>82</v>
+        <v>689</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>82</v>
+        <v>690</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22444,19 +22597,19 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>167</v>
+        <v>686</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>82</v>
@@ -22474,19 +22627,19 @@
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -22499,25 +22652,25 @@
         <v>82</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>299</v>
+        <v>693</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>300</v>
+        <v>694</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>139</v>
+        <v>695</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>145</v>
+        <v>696</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22542,13 +22695,13 @@
         <v>82</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>82</v>
+        <v>697</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>82</v>
+        <v>698</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22566,7 +22719,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>301</v>
+        <v>692</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22578,7 +22731,7 @@
         <v>82</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>82</v>
@@ -22590,21 +22743,21 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>133</v>
+        <v>699</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>82</v>
+        <v>700</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22612,13 +22765,13 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>82</v>
@@ -22627,13 +22780,13 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>714</v>
+        <v>179</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22660,13 +22813,13 @@
         <v>82</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>82</v>
+        <v>704</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>82</v>
+        <v>705</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22684,13 +22837,13 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>82</v>
@@ -22699,30 +22852,30 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>717</v>
+        <v>82</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>718</v>
+        <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>719</v>
+        <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>465</v>
+        <v>706</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>720</v>
+        <v>82</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>721</v>
+        <v>707</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22733,7 +22886,7 @@
         <v>80</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>82</v>
@@ -22745,17 +22898,15 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>725</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22780,13 +22931,13 @@
         <v>82</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>727</v>
+        <v>712</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22804,13 +22955,13 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>82</v>
@@ -22828,21 +22979,21 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>728</v>
+        <v>713</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>82</v>
+        <v>714</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22865,17 +23016,15 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>179</v>
+        <v>630</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22900,13 +23049,13 @@
         <v>82</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>733</v>
+        <v>82</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>734</v>
+        <v>82</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -22924,7 +23073,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22948,21 +23097,21 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>82</v>
+        <v>718</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>82</v>
+        <v>719</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22985,13 +23134,13 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>736</v>
+        <v>159</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>737</v>
+        <v>160</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23042,7 +23191,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>735</v>
+        <v>161</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -23054,7 +23203,7 @@
         <v>82</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>82</v>
@@ -23066,7 +23215,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>457</v>
+        <v>162</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -23077,24 +23226,24 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>82</v>
@@ -23103,15 +23252,17 @@
         <v>82</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>739</v>
+        <v>136</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>740</v>
+        <v>137</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N171" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -23148,57 +23299,57 @@
         <v>82</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>738</v>
+        <v>167</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>742</v>
+        <v>82</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>718</v>
+        <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>743</v>
+        <v>162</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23218,19 +23369,19 @@
         <v>82</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>746</v>
+        <v>158</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>747</v>
+        <v>637</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>748</v>
+        <v>638</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>749</v>
+        <v>639</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23280,7 +23431,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>745</v>
+        <v>640</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23289,7 +23440,7 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
@@ -23301,20 +23452,3016 @@
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP173" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AO174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP174" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="175" hidden="true">
+      <c r="A175" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP175" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="176" hidden="true">
+      <c r="A176" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP176" t="s" s="2">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="177" hidden="true">
+      <c r="A177" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
+      <c r="P177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q177" s="2"/>
+      <c r="R177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP177" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O178" s="2"/>
+      <c r="P178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q178" s="2"/>
+      <c r="R178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN178" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP178" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="179" hidden="true">
+      <c r="A179" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="P179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q179" s="2"/>
+      <c r="R179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN179" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AO179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP179" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="180" hidden="true">
+      <c r="A180" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G180" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N180" s="2"/>
+      <c r="O180" s="2"/>
+      <c r="P180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q180" s="2"/>
+      <c r="R180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN180" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP180" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="181" hidden="true">
+      <c r="A181" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O181" s="2"/>
+      <c r="P181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q181" s="2"/>
+      <c r="R181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN181" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP181" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="182" hidden="true">
+      <c r="A182" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="C182" s="2"/>
+      <c r="D182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G182" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H182" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J182" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K182" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="P182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q182" s="2"/>
+      <c r="R182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S182" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF182" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG182" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH182" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ182" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK182" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="AL182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN182" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO182" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP182" t="s" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="183" hidden="true">
+      <c r="A183" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="C183" s="2"/>
+      <c r="D183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G183" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="O183" s="2"/>
+      <c r="P183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q183" s="2"/>
+      <c r="R183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN183" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AO183" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP183" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="184" hidden="true">
+      <c r="A184" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="C184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G184" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N184" s="2"/>
+      <c r="O184" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q184" s="2"/>
+      <c r="R184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK184" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AL184" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AM184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN184" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO184" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP184" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="185" hidden="true">
+      <c r="A185" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="C185" s="2"/>
+      <c r="D185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E185" s="2"/>
+      <c r="F185" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G185" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J185" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K185" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M185" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N185" s="2"/>
+      <c r="O185" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q185" s="2"/>
+      <c r="R185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ185" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN185" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP185" t="s" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="186" hidden="true">
+      <c r="A186" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="P186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q186" s="2"/>
+      <c r="R186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN186" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AO186" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP186" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="187" hidden="true">
+      <c r="A187" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN187" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AO187" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP187" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="188" hidden="true">
+      <c r="A188" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="AN172" t="s" s="2">
+      <c r="B188" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H188" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K188" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L188" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="AO172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP172" t="s" s="2">
+      <c r="M188" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="O188" s="2"/>
+      <c r="P188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q188" s="2"/>
+      <c r="R188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF188" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AG188" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH188" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ188" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN188" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AO188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP188" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="189" hidden="true">
+      <c r="A189" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C189" s="2"/>
+      <c r="D189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G189" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K189" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N189" s="2"/>
+      <c r="O189" s="2"/>
+      <c r="P189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q189" s="2"/>
+      <c r="R189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF189" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG189" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH189" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN189" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP189" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="190" hidden="true">
+      <c r="A190" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O190" s="2"/>
+      <c r="P190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q190" s="2"/>
+      <c r="R190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN190" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP190" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="191" hidden="true">
+      <c r="A191" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="C191" s="2"/>
+      <c r="D191" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I191" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J191" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K191" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L191" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q191" s="2"/>
+      <c r="R191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF191" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN191" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP191" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="192" hidden="true">
+      <c r="A192" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="N192" s="2"/>
+      <c r="O192" s="2"/>
+      <c r="P192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q192" s="2"/>
+      <c r="R192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK192" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AL192" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AN192" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AO192" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AP192" t="s" s="2">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="193" hidden="true">
+      <c r="A193" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K193" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="O193" s="2"/>
+      <c r="P193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q193" s="2"/>
+      <c r="R193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN193" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AO193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP193" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="194" hidden="true">
+      <c r="A194" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="O194" s="2"/>
+      <c r="P194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP194" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="195" hidden="true">
+      <c r="A195" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G195" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K195" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N195" s="2"/>
+      <c r="O195" s="2"/>
+      <c r="P195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q195" s="2"/>
+      <c r="R195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF195" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ195" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN195" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP195" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="196" hidden="true">
+      <c r="A196" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="C196" s="2"/>
+      <c r="D196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E196" s="2"/>
+      <c r="F196" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G196" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H196" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K196" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="L196" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M196" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N196" s="2"/>
+      <c r="O196" s="2"/>
+      <c r="P196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q196" s="2"/>
+      <c r="R196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF196" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AG196" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH196" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ196" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK196" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AL196" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AM196" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN196" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AO196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP196" t="s" s="2">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="197" hidden="true">
+      <c r="A197" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="C197" s="2"/>
+      <c r="D197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E197" s="2"/>
+      <c r="F197" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G197" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K197" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="L197" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M197" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="N197" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="O197" s="2"/>
+      <c r="P197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q197" s="2"/>
+      <c r="R197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF197" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AG197" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH197" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ197" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM197" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="AN197" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AO197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP197" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP172">
+  <autoFilter ref="A1:AP197">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -23324,7 +26471,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI171">
+  <conditionalFormatting sqref="A2:AI196">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -801,10 +801,10 @@
     <t>Encounter.identifier:va-IEN.system</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/VistADefinedTerms/45-.001</t>
-  </si>
-  <si>
-    <t>427-1: fixed value = http://va.gov/terminology/VistADefinedTerms/45-.001</t>
+    <t>http://va.gov/fhir/identiiers/Sta3n$stationNr/45</t>
+  </si>
+  <si>
+    <t>427-1: fixed value = http://va.gov/fhir/identiiers/Sta3n$stationNr/45</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IEN.value</t>
@@ -858,10 +858,10 @@
     <t>Encounter.identifier:va-IA.system</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/VistADefinedTerms/45-2.1</t>
-  </si>
-  <si>
-    <t>428-1: fixed value = http://va.gov/terminology/VistADefinedTerms/45-2.1</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/45-2.1</t>
+  </si>
+  <si>
+    <t>428-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/45-2.1</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IA.value</t>
@@ -1715,37 +1715,37 @@
     <t>Encounter.reasonCode.text</t>
   </si>
   <si>
-    <t>Encounter.reasonCode:va-secundary</t>
-  </si>
-  <si>
-    <t>va-secundary</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.id</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.extension</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.coding</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.coding.system</t>
+    <t>Encounter.reasonCode:va-secondary</t>
+  </si>
+  <si>
+    <t>va-secondary</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.coding</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.coding.system</t>
   </si>
   <si>
     <t>449-1: fixed value = urn:see-termmap-in-mapParameter</t>
   </si>
   <si>
-    <t>Encounter.reasonCode:va-secundary.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.coding.code</t>
+    <t>Encounter.reasonCode:va-secondary.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.coding.code</t>
   </si>
   <si>
     <t>449: source value from PTF - SECONDARY DIAGNOSIS [#] (45-79.16)</t>
@@ -1754,13 +1754,13 @@
     <t>Inpat.CensusDiagnosis.ICDIEN,Inpat.InpatientDiagnosis.ICDIEN</t>
   </si>
   <si>
-    <t>Encounter.reasonCode:va-secundary.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.reasonCode:va-secundary.text</t>
+    <t>Encounter.reasonCode:va-secondary.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.reasonCode:va-secondary.text</t>
   </si>
   <si>
     <t>Encounter.reasonCode:va-procedure</t>
@@ -2795,7 +2795,7 @@
   <cols>
     <col min="1" max="1" width="63.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="63.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.45703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -801,10 +801,10 @@
     <t>Encounter.identifier:va-IEN.system</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identiiers/Sta3n$stationNr/45</t>
-  </si>
-  <si>
-    <t>427-1: fixed value = http://va.gov/fhir/identiiers/Sta3n$stationNr/45</t>
+    <t>http://va.gov/fhir/identiiers/$Sta3n/45</t>
+  </si>
+  <si>
+    <t>427-1: fixed value = http://va.gov/fhir/identiiers/$Sta3n/45</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IEN.value</t>
@@ -858,10 +858,10 @@
     <t>Encounter.identifier:va-IA.system</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/45-2.1</t>
-  </si>
-  <si>
-    <t>428-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/45-2.1</t>
+    <t>http://va.gov/identifiers/$Sta3n/45-2.1</t>
+  </si>
+  <si>
+    <t>428-1: fixed value = http://va.gov/identifiers/$Sta3n/45-2.1</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IA.value</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="796">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -801,10 +801,10 @@
     <t>Encounter.identifier:va-IEN.system</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identiiers/$Sta3n/45</t>
-  </si>
-  <si>
-    <t>427-1: fixed value = http://va.gov/fhir/identiiers/$Sta3n/45</t>
+    <t>http://va.gov/identifiers/$Sta3n/45</t>
+  </si>
+  <si>
+    <t>427-1: fixed value = http://va.gov/identifiers/$Sta3n/45</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IEN.value</t>
@@ -1849,7 +1849,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterInpatientCondition)
+    <t xml:space="preserve">Reference(Condition|Procedure)
 </t>
   </si>
   <si>
@@ -1857,9 +1857,6 @@
   </si>
   <si>
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
-  </si>
-  <si>
-    <t>1723: reference</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -19181,7 +19178,7 @@
         <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>82</v>
@@ -19264,30 +19261,30 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AL137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM137" t="s" s="2">
+      <c r="AN137" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>520</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19313,10 +19310,10 @@
         <v>179</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19346,11 +19343,11 @@
         <v>114</v>
       </c>
       <c r="Y138" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="Z138" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="Z138" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19367,7 +19364,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19402,10 +19399,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19428,13 +19425,13 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19485,7 +19482,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19509,7 +19506,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -19520,10 +19517,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19546,16 +19543,16 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19605,7 +19602,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19629,7 +19626,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19640,10 +19637,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19669,13 +19666,13 @@
         <v>291</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19725,7 +19722,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19749,7 +19746,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19760,10 +19757,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19878,10 +19875,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19998,10 +19995,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20120,10 +20117,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20149,10 +20146,10 @@
         <v>148</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20203,7 +20200,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20233,15 +20230,15 @@
         <v>82</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20264,13 +20261,13 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20321,7 +20318,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20345,7 +20342,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20356,10 +20353,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20474,10 +20471,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20594,10 +20591,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20623,13 +20620,13 @@
         <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20679,16 +20676,16 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI149" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>102</v>
@@ -20714,10 +20711,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20743,13 +20740,13 @@
         <v>104</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20778,28 +20775,28 @@
         <v>184</v>
       </c>
       <c r="Y150" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="Z150" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="Z150" t="s" s="2">
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20834,10 +20831,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20863,13 +20860,13 @@
         <v>148</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20919,7 +20916,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20943,7 +20940,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20954,10 +20951,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20983,13 +20980,13 @@
         <v>158</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21039,7 +21036,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21054,10 +21051,10 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL152" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
@@ -21074,10 +21071,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21103,10 +21100,10 @@
         <v>179</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21136,11 +21133,11 @@
         <v>114</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="Z153" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="Z153" t="s" s="2">
-        <v>666</v>
-      </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
       </c>
@@ -21157,7 +21154,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21181,21 +21178,21 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP153" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP153" t="s" s="2">
-        <v>668</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21310,10 +21307,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21430,10 +21427,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21497,7 +21494,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21530,10 +21527,10 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AL156" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
@@ -21550,10 +21547,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21668,10 +21665,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21788,10 +21785,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21836,7 +21833,7 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>82</v>
@@ -21890,7 +21887,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -21910,10 +21907,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22030,10 +22027,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22130,10 +22127,10 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
@@ -22150,10 +22147,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22270,10 +22267,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22392,10 +22389,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22514,10 +22511,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22543,10 +22540,10 @@
         <v>179</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22576,11 +22573,11 @@
         <v>393</v>
       </c>
       <c r="Y165" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="Z165" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="Z165" t="s" s="2">
-        <v>690</v>
-      </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
       </c>
@@ -22597,7 +22594,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22627,15 +22624,15 @@
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22661,16 +22658,16 @@
         <v>179</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22698,11 +22695,11 @@
         <v>393</v>
       </c>
       <c r="Y166" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="Z166" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="Z166" t="s" s="2">
-        <v>698</v>
-      </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
       </c>
@@ -22719,7 +22716,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22743,21 +22740,21 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP166" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP166" t="s" s="2">
-        <v>700</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22783,10 +22780,10 @@
         <v>179</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22816,11 +22813,11 @@
         <v>114</v>
       </c>
       <c r="Y167" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z167" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="Z167" t="s" s="2">
-        <v>705</v>
-      </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
       </c>
@@ -22837,7 +22834,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22861,21 +22858,21 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP167" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>707</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22901,10 +22898,10 @@
         <v>179</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22934,11 +22931,11 @@
         <v>114</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="Z168" t="s" s="2">
-        <v>712</v>
-      </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
       </c>
@@ -22955,7 +22952,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22979,21 +22976,21 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP168" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP168" t="s" s="2">
-        <v>714</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23016,13 +23013,13 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23073,7 +23070,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23097,21 +23094,21 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP169" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP169" t="s" s="2">
-        <v>719</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23226,10 +23223,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23346,10 +23343,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23375,13 +23372,13 @@
         <v>158</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23431,16 +23428,16 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI172" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AG172" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH172" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI172" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
@@ -23466,10 +23463,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23495,13 +23492,13 @@
         <v>104</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23530,28 +23527,28 @@
         <v>184</v>
       </c>
       <c r="Y173" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="Z173" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="Z173" t="s" s="2">
+      <c r="AA173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF173" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AA173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF173" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23586,10 +23583,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23615,13 +23612,13 @@
         <v>148</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23671,7 +23668,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23695,7 +23692,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23706,10 +23703,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23735,13 +23732,13 @@
         <v>158</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23791,7 +23788,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23806,10 +23803,10 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AL175" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="AL175" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
@@ -23826,10 +23823,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23855,10 +23852,10 @@
         <v>179</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23888,11 +23885,11 @@
         <v>114</v>
       </c>
       <c r="Y176" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="Z176" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="Z176" t="s" s="2">
-        <v>732</v>
-      </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23909,7 +23906,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23933,21 +23930,21 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP176" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP176" t="s" s="2">
-        <v>734</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24062,10 +24059,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24182,10 +24179,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24304,10 +24301,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24422,10 +24419,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24542,10 +24539,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24590,7 +24587,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24644,7 +24641,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>82</v>
@@ -24664,10 +24661,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24784,10 +24781,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24884,10 +24881,10 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AL184" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="AL184" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>82</v>
@@ -24904,10 +24901,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25024,10 +25021,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25146,10 +25143,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25268,10 +25265,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25297,13 +25294,13 @@
         <v>291</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25353,7 +25350,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25377,7 +25374,7 @@
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
@@ -25388,10 +25385,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25506,10 +25503,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25626,10 +25623,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25748,10 +25745,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25774,13 +25771,13 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="L192" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="L192" t="s" s="2">
+      <c r="M192" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25831,7 +25828,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>90</v>
@@ -25846,30 +25843,30 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="AL192" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="AL192" t="s" s="2">
+      <c r="AM192" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>465</v>
       </c>
       <c r="AO192" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AP192" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="AP192" t="s" s="2">
-        <v>766</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25895,13 +25892,13 @@
         <v>110</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25930,11 +25927,11 @@
         <v>173</v>
       </c>
       <c r="Y193" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="Z193" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="Z193" t="s" s="2">
-        <v>772</v>
-      </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
       </c>
@@ -25951,7 +25948,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25975,7 +25972,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25986,10 +25983,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26015,13 +26012,13 @@
         <v>179</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26050,11 +26047,11 @@
         <v>393</v>
       </c>
       <c r="Y194" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="Z194" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="Z194" t="s" s="2">
-        <v>779</v>
-      </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
       </c>
@@ -26071,7 +26068,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26106,10 +26103,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26135,10 +26132,10 @@
         <v>207</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26189,7 +26186,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26224,10 +26221,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26250,13 +26247,13 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="L196" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="M196" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26307,7 +26304,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26322,30 +26319,30 @@
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>464</v>
       </c>
       <c r="AN196" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AO196" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP196" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP196" t="s" s="2">
-        <v>789</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26368,16 +26365,16 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="L197" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="L197" t="s" s="2">
+      <c r="M197" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="M197" t="s" s="2">
+      <c r="N197" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -26427,7 +26424,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26448,10 +26445,10 @@
         <v>82</v>
       </c>
       <c r="AM197" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AN197" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="AN197" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="798">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1849,7 +1849,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterInpatientCondition)
 </t>
   </si>
   <si>
@@ -1857,6 +1857,9 @@
   </si>
   <si>
     <t>Reason the encounter takes place, as specified using information from another resource. For admissions, this is the admission diagnosis. The indication will typically be a Condition (with other resources referenced in the evidence.detail), or a Procedure.</t>
+  </si>
+  <si>
+    <t>1723: reference</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1894,6 +1897,9 @@
   </si>
   <si>
     <t>Ranking of the diagnosis (for each role type).</t>
+  </si>
+  <si>
+    <t>1723-1: fixed value = 1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON].priority</t>
@@ -19178,7 +19184,7 @@
         <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>82</v>
@@ -19261,30 +19267,30 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>520</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19310,10 +19316,10 @@
         <v>179</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19343,10 +19349,10 @@
         <v>114</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -19364,7 +19370,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19399,10 +19405,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19416,7 +19422,7 @@
         <v>90</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>82</v>
@@ -19425,13 +19431,13 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19443,7 +19449,7 @@
         <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>82</v>
@@ -19482,7 +19488,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19497,7 +19503,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -19506,7 +19512,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -19517,10 +19523,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19543,16 +19549,16 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19602,7 +19608,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19626,7 +19632,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19637,10 +19643,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19666,13 +19672,13 @@
         <v>291</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19722,7 +19728,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19746,7 +19752,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19757,10 +19763,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19875,10 +19881,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19995,10 +20001,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20117,10 +20123,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20146,10 +20152,10 @@
         <v>148</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20200,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20230,15 +20236,15 @@
         <v>82</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20261,13 +20267,13 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20318,7 +20324,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20342,7 +20348,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20353,10 +20359,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20471,10 +20477,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20591,10 +20597,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20620,13 +20626,13 @@
         <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20676,7 +20682,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20685,7 +20691,7 @@
         <v>90</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>102</v>
@@ -20711,10 +20717,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20740,13 +20746,13 @@
         <v>104</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20775,10 +20781,10 @@
         <v>184</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20796,7 +20802,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20831,10 +20837,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20860,13 +20866,13 @@
         <v>148</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20916,7 +20922,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20940,7 +20946,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20951,10 +20957,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20980,13 +20986,13 @@
         <v>158</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21036,7 +21042,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21051,10 +21057,10 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
@@ -21071,10 +21077,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21100,10 +21106,10 @@
         <v>179</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21133,10 +21139,10 @@
         <v>114</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -21154,7 +21160,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21178,21 +21184,21 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21307,10 +21313,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21427,10 +21433,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21494,7 +21500,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21527,10 +21533,10 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
@@ -21547,10 +21553,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21665,10 +21671,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21785,10 +21791,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21833,7 +21839,7 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>82</v>
@@ -21887,7 +21893,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -21907,10 +21913,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22027,10 +22033,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22127,10 +22133,10 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
@@ -22147,10 +22153,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22267,10 +22273,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22389,10 +22395,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22511,10 +22517,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22540,10 +22546,10 @@
         <v>179</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22573,10 +22579,10 @@
         <v>393</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22594,7 +22600,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22624,15 +22630,15 @@
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22658,16 +22664,16 @@
         <v>179</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22695,10 +22701,10 @@
         <v>393</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22716,7 +22722,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22740,21 +22746,21 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22780,10 +22786,10 @@
         <v>179</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22813,10 +22819,10 @@
         <v>114</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22834,7 +22840,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22858,21 +22864,21 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22898,10 +22904,10 @@
         <v>179</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22931,10 +22937,10 @@
         <v>114</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22952,7 +22958,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22976,21 +22982,21 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23013,13 +23019,13 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23070,7 +23076,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23094,21 +23100,21 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23223,10 +23229,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23343,10 +23349,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23372,13 +23378,13 @@
         <v>158</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23428,7 +23434,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23437,7 +23443,7 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
@@ -23463,10 +23469,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23492,13 +23498,13 @@
         <v>104</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23527,10 +23533,10 @@
         <v>184</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -23548,7 +23554,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23583,10 +23589,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23612,13 +23618,13 @@
         <v>148</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23668,7 +23674,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23692,7 +23698,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23703,10 +23709,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23732,13 +23738,13 @@
         <v>158</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23788,7 +23794,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23803,10 +23809,10 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
@@ -23823,10 +23829,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23852,10 +23858,10 @@
         <v>179</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23885,10 +23891,10 @@
         <v>114</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
@@ -23906,7 +23912,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23930,21 +23936,21 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24059,10 +24065,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24179,10 +24185,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24301,10 +24307,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24419,10 +24425,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24539,10 +24545,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24587,7 +24593,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24641,7 +24647,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>82</v>
@@ -24661,10 +24667,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24781,10 +24787,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24881,10 +24887,10 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>82</v>
@@ -24901,10 +24907,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25021,10 +25027,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25143,10 +25149,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25265,10 +25271,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25294,13 +25300,13 @@
         <v>291</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25350,7 +25356,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25374,7 +25380,7 @@
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
@@ -25385,10 +25391,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25503,10 +25509,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25623,10 +25629,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25745,10 +25751,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25771,13 +25777,13 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25828,7 +25834,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>90</v>
@@ -25843,30 +25849,30 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>465</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25892,13 +25898,13 @@
         <v>110</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25927,10 +25933,10 @@
         <v>173</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25948,7 +25954,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25972,7 +25978,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25983,10 +25989,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26012,13 +26018,13 @@
         <v>179</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26047,10 +26053,10 @@
         <v>393</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -26068,7 +26074,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26103,10 +26109,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26132,10 +26138,10 @@
         <v>207</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26186,7 +26192,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26221,10 +26227,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26247,13 +26253,13 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26304,7 +26310,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26319,30 +26325,30 @@
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>464</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP196" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26365,16 +26371,16 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -26424,7 +26430,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26445,10 +26451,10 @@
         <v>82</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1439,7 +1439,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -2436,7 +2436,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="799">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1748,10 +1748,10 @@
     <t>Encounter.reasonCode:va-secondary.coding.code</t>
   </si>
   <si>
-    <t>449: source value from PTF - SECONDARY DIAGNOSIS [#] (45-79.16)</t>
-  </si>
-  <si>
-    <t>Inpat.CensusDiagnosis.ICDIEN,Inpat.InpatientDiagnosis.ICDIEN</t>
+    <t>449: source value from PTF - SECONDARY DIAGNOSIS 1-24 &gt; ICD DIAGNOSIS - CODE NUMBER (45-79.* &gt; 80-.01)</t>
+  </si>
+  <si>
+    <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
   </si>
   <si>
     <t>Encounter.reasonCode:va-secondary.coding.display</t>
@@ -1799,7 +1799,10 @@
     <t>Encounter.reasonCode:va-procedure.coding.code</t>
   </si>
   <si>
-    <t>450: source value from PTF - PROCEDURE [#] (45-45.01)</t>
+    <t>450: source value from PTF - PROCEDURE 1-5 &gt; ICD OPERATION/PROCEDURE - CODE NUMBER (45-45.01+to+45.05 &gt; 80.1-.01)</t>
+  </si>
+  <si>
+    <t>Dim.ICD10Procedure.ICD10ProcedureCode,Dim.ICD9Procedure.ICD9ProcedureCode</t>
   </si>
   <si>
     <t>Encounter.reasonCode:va-procedure.coding.display</t>
@@ -18188,7 +18191,7 @@
         <v>578</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
@@ -18205,7 +18208,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>545</v>
@@ -18325,7 +18328,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>547</v>
@@ -18447,7 +18450,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>549</v>
@@ -18569,10 +18572,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18595,10 +18598,10 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M132" t="s" s="2">
         <v>514</v>
@@ -18654,7 +18657,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18689,10 +18692,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18718,10 +18721,10 @@
         <v>291</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18772,7 +18775,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18796,7 +18799,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18807,10 +18810,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18925,10 +18928,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19045,10 +19048,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19167,14 +19170,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -19193,13 +19196,13 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>515</v>
@@ -19252,7 +19255,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>90</v>
@@ -19267,30 +19270,30 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>520</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19316,10 +19319,10 @@
         <v>179</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19349,10 +19352,10 @@
         <v>114</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -19370,7 +19373,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19405,10 +19408,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19431,13 +19434,13 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19488,7 +19491,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19503,7 +19506,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -19512,7 +19515,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -19523,10 +19526,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19549,16 +19552,16 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19608,7 +19611,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19632,7 +19635,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19643,10 +19646,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19672,13 +19675,13 @@
         <v>291</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19728,7 +19731,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19752,7 +19755,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19763,10 +19766,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19881,10 +19884,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20001,10 +20004,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20123,10 +20126,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20152,10 +20155,10 @@
         <v>148</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20206,7 +20209,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20236,15 +20239,15 @@
         <v>82</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20267,13 +20270,13 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20324,7 +20327,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20348,7 +20351,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20359,10 +20362,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20477,10 +20480,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20597,10 +20600,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20626,13 +20629,13 @@
         <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20682,7 +20685,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20691,7 +20694,7 @@
         <v>90</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>102</v>
@@ -20717,10 +20720,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20746,13 +20749,13 @@
         <v>104</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20781,10 +20784,10 @@
         <v>184</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20802,7 +20805,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20837,10 +20840,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20866,13 +20869,13 @@
         <v>148</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20922,7 +20925,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20946,7 +20949,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -20957,10 +20960,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20986,13 +20989,13 @@
         <v>158</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21042,7 +21045,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21057,10 +21060,10 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
@@ -21077,10 +21080,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21106,10 +21109,10 @@
         <v>179</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21139,10 +21142,10 @@
         <v>114</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -21160,7 +21163,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21184,21 +21187,21 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21313,10 +21316,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21433,10 +21436,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21500,7 +21503,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21533,10 +21536,10 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
@@ -21553,10 +21556,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21671,10 +21674,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21791,10 +21794,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21839,7 +21842,7 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>82</v>
@@ -21893,7 +21896,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -21913,10 +21916,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22033,10 +22036,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22133,10 +22136,10 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
@@ -22153,10 +22156,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22273,10 +22276,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22395,10 +22398,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22517,10 +22520,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22546,10 +22549,10 @@
         <v>179</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22579,10 +22582,10 @@
         <v>393</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22600,7 +22603,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22630,15 +22633,15 @@
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22664,16 +22667,16 @@
         <v>179</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22701,10 +22704,10 @@
         <v>393</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22722,7 +22725,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22746,21 +22749,21 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22786,10 +22789,10 @@
         <v>179</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22819,10 +22822,10 @@
         <v>114</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22840,7 +22843,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22864,21 +22867,21 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22904,10 +22907,10 @@
         <v>179</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22937,10 +22940,10 @@
         <v>114</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22958,7 +22961,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22982,21 +22985,21 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23019,13 +23022,13 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23076,7 +23079,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23100,21 +23103,21 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23229,10 +23232,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23349,10 +23352,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23378,13 +23381,13 @@
         <v>158</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23434,7 +23437,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23443,7 +23446,7 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
@@ -23469,10 +23472,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23498,13 +23501,13 @@
         <v>104</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23533,10 +23536,10 @@
         <v>184</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -23554,7 +23557,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23589,10 +23592,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23618,13 +23621,13 @@
         <v>148</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23674,7 +23677,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23698,7 +23701,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23709,10 +23712,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23738,13 +23741,13 @@
         <v>158</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23794,7 +23797,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23809,10 +23812,10 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
@@ -23829,10 +23832,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23858,10 +23861,10 @@
         <v>179</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23891,10 +23894,10 @@
         <v>114</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
@@ -23912,7 +23915,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23936,21 +23939,21 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24065,10 +24068,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24185,10 +24188,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24307,10 +24310,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24425,10 +24428,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24545,10 +24548,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24593,7 +24596,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24647,7 +24650,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>82</v>
@@ -24667,10 +24670,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24787,10 +24790,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24887,10 +24890,10 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>82</v>
@@ -24907,10 +24910,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25027,10 +25030,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25149,10 +25152,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25271,10 +25274,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25300,13 +25303,13 @@
         <v>291</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25356,7 +25359,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25380,7 +25383,7 @@
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
@@ -25391,10 +25394,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25509,10 +25512,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25629,10 +25632,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25751,10 +25754,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25777,13 +25780,13 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25834,7 +25837,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>90</v>
@@ -25849,30 +25852,30 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>465</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25898,13 +25901,13 @@
         <v>110</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25933,10 +25936,10 @@
         <v>173</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25954,7 +25957,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25978,7 +25981,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25989,10 +25992,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26018,13 +26021,13 @@
         <v>179</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26053,10 +26056,10 @@
         <v>393</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -26074,7 +26077,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26109,10 +26112,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26138,10 +26141,10 @@
         <v>207</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26192,7 +26195,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26227,10 +26230,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26253,13 +26256,13 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26310,7 +26313,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26325,30 +26328,30 @@
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>464</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP196" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26371,16 +26374,16 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -26430,7 +26433,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26451,10 +26454,10 @@
         <v>82</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -1439,7 +1439,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1270,7 +1270,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2362,7 +2362,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$213</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7515" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8120" uniqueCount="820">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2100,7 +2100,7 @@
     <t>Encounter.hospitalization.admitSource.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFSourceOfAdmission</t>
+    <t>http://va.gov/fhir/ValueSet/SourceOfAdmission</t>
   </si>
   <si>
     <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
@@ -2362,14 +2362,128 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Location the encounter takes place</t>
+  </si>
+  <si>
+    <t>The location where the encounter takes place.</t>
+  </si>
+  <si>
+    <t>Event.location</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
+  </si>
+  <si>
+    <t>Encounter.location.status</t>
+  </si>
+  <si>
+    <t>planned | active | reserved | completed</t>
+  </si>
+  <si>
+    <t>The status of the participants' presence at the specified location during the period specified. If the participant is no longer at the location, then the period will have an end date/time.</t>
+  </si>
+  <si>
+    <t>When the patient is no longer active at a location, then the period end date is entered, and the status may be changed to completed.</t>
+  </si>
+  <si>
+    <t>The status of the location.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-location-status|4.0.1</t>
+  </si>
+  <si>
+    <t>.role.statusCode</t>
+  </si>
+  <si>
+    <t>Encounter.location.physicalType</t>
+  </si>
+  <si>
+    <t>The physical type of the location (usually the level in the location hierachy - bed room ward etc.)</t>
+  </si>
+  <si>
+    <t>This will be used to specify the required levels (bed/ward/room/etc.) desired to be recorded to simplify either messaging or query.</t>
+  </si>
+  <si>
+    <t>This information is de-normalized from the Location resource to support the easier understanding of the encounter resource and processing in messaging or query.
+There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
+  </si>
+  <si>
+    <t>Physical form of the location.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+  </si>
+  <si>
+    <t>Encounter.location.period</t>
+  </si>
+  <si>
+    <t>Time period during which the patient was present at the location</t>
+  </si>
+  <si>
+    <t>Time period during which the patient was present at the location.</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward</t>
+  </si>
+  <si>
+    <t>va-ward</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.id</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.extension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.location</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Location)
 </t>
   </si>
   <si>
-    <t>Location the encounter takes place</t>
-  </si>
-  <si>
-    <t>The location where the encounter takes place.</t>
+    <t>460: reference from PTF - WARD AT DISCHARGE &gt; WARD LOCATION - HOSPITAL LOCATION FILE POINTER (45-2.2 &gt; 42-44)</t>
+  </si>
+  <si>
+    <t>Inpat.Inpatient.Discharge45WardLocationIEN
+Dim.WardLocation.LocationIEN</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.status</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.physicalType</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-ward.period</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility</t>
+  </si>
+  <si>
+    <t>va-facility</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility.id</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility.extension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility.location</t>
   </si>
   <si>
     <t>461: reference from PTF - FACILITY (45-3)</t>
@@ -2378,62 +2492,13 @@
     <t>Inpat.Census.DischargeFacility,Inpat.Inpatient.DischargeFromFacility,Inpat.InpatientFeeBasis.DischargeFacility</t>
   </si>
   <si>
-    <t>Event.location</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
-  </si>
-  <si>
-    <t>Encounter.location.status</t>
-  </si>
-  <si>
-    <t>planned | active | reserved | completed</t>
-  </si>
-  <si>
-    <t>The status of the participants' presence at the specified location during the period specified. If the participant is no longer at the location, then the period will have an end date/time.</t>
-  </si>
-  <si>
-    <t>When the patient is no longer active at a location, then the period end date is entered, and the status may be changed to completed.</t>
-  </si>
-  <si>
-    <t>The status of the location.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-location-status|4.0.1</t>
-  </si>
-  <si>
-    <t>.role.statusCode</t>
-  </si>
-  <si>
-    <t>Encounter.location.physicalType</t>
-  </si>
-  <si>
-    <t>The physical type of the location (usually the level in the location hierachy - bed room ward etc.)</t>
-  </si>
-  <si>
-    <t>This will be used to specify the required levels (bed/ward/room/etc.) desired to be recorded to simplify either messaging or query.</t>
-  </si>
-  <si>
-    <t>This information is de-normalized from the Location resource to support the easier understanding of the encounter resource and processing in messaging or query.
-There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
-  </si>
-  <si>
-    <t>Physical form of the location.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
-  </si>
-  <si>
-    <t>Encounter.location.period</t>
-  </si>
-  <si>
-    <t>Time period during which the patient was present at the location</t>
-  </si>
-  <si>
-    <t>Time period during which the patient was present at the location.</t>
+    <t>Encounter.location:va-facility.status</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility.physicalType</t>
+  </si>
+  <si>
+    <t>Encounter.location:va-facility.period</t>
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
@@ -2796,7 +2861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP197"/>
+  <dimension ref="A1:AP213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.30078125" customWidth="true" bestFit="true"/>
@@ -25347,16 +25412,14 @@
         <v>82</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="AC188" s="2"/>
       <c r="AD188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE188" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="AF188" t="s" s="2">
         <v>752</v>
@@ -25852,30 +25915,30 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM192" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>465</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25901,13 +25964,13 @@
         <v>110</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="N193" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25936,10 +25999,10 @@
         <v>173</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25957,7 +26020,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25981,7 +26044,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25992,10 +26055,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26021,13 +26084,13 @@
         <v>179</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26056,10 +26119,10 @@
         <v>393</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -26077,7 +26140,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26112,10 +26175,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26141,10 +26204,10 @@
         <v>207</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26195,7 +26258,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26230,12 +26293,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="C196" s="2"/>
+        <v>752</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>784</v>
+      </c>
       <c r="D196" t="s" s="2">
         <v>82</v>
       </c>
@@ -26256,15 +26321,17 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>786</v>
+        <v>291</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>787</v>
+        <v>753</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="N196" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="N196" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>82</v>
@@ -26313,13 +26380,13 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>785</v>
+        <v>752</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>82</v>
@@ -26328,30 +26395,30 @@
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>789</v>
+        <v>82</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>765</v>
+        <v>82</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>790</v>
+        <v>756</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP196" t="s" s="2">
-        <v>791</v>
+        <v>82</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>792</v>
+        <v>757</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26374,17 +26441,15 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>793</v>
+        <v>158</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>794</v>
+        <v>159</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>796</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>82</v>
@@ -26433,41 +26498,1955 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG197" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH197" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN197" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO197" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP197" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="198" hidden="true">
+      <c r="A198" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C198" s="2"/>
+      <c r="D198" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E198" s="2"/>
+      <c r="F198" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G198" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K198" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L198" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M198" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O198" s="2"/>
+      <c r="P198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q198" s="2"/>
+      <c r="R198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF198" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG198" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH198" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ198" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN198" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO198" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP198" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="199" hidden="true">
+      <c r="A199" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C199" s="2"/>
+      <c r="D199" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E199" s="2"/>
+      <c r="F199" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G199" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I199" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J199" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K199" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L199" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M199" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O199" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q199" s="2"/>
+      <c r="R199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF199" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG199" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH199" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ199" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN199" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO199" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP199" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="200" hidden="true">
+      <c r="A200" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C200" s="2"/>
+      <c r="D200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E200" s="2"/>
+      <c r="F200" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G200" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H200" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K200" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="L200" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="M200" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
+      <c r="P200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q200" s="2"/>
+      <c r="R200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF200" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="AG200" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH200" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI200" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ200" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK200" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AL200" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="AM200" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AN200" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AO200" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AP200" t="s" s="2">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="201" hidden="true">
+      <c r="A201" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="AG197" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
+      <c r="B201" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C201" s="2"/>
+      <c r="D201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E201" s="2"/>
+      <c r="F201" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G201" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K201" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L201" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M201" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="N201" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="O201" s="2"/>
+      <c r="P201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q201" s="2"/>
+      <c r="R201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X201" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y201" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="Z201" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AA201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF201" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AG201" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH201" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ201" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM197" t="s" s="2">
+      <c r="AK201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN201" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AO201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP201" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="202" hidden="true">
+      <c r="A202" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C202" s="2"/>
+      <c r="D202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E202" s="2"/>
+      <c r="F202" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G202" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K202" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L202" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M202" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="O202" s="2"/>
+      <c r="P202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q202" s="2"/>
+      <c r="R202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X202" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Y202" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="Z202" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AA202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF202" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AG202" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH202" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ202" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO202" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP202" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="203" hidden="true">
+      <c r="A203" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C203" s="2"/>
+      <c r="D203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E203" s="2"/>
+      <c r="F203" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G203" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K203" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L203" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M203" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
+      <c r="P203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q203" s="2"/>
+      <c r="R203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF203" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG203" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH203" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ203" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN203" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO203" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP203" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="204" hidden="true">
+      <c r="A204" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="C204" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="D204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E204" s="2"/>
+      <c r="F204" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G204" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H204" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K204" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L204" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="M204" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="N204" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="O204" s="2"/>
+      <c r="P204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q204" s="2"/>
+      <c r="R204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF204" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AG204" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH204" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ204" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN204" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AO204" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP204" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="205" hidden="true">
+      <c r="A205" t="s" s="2">
         <v>797</v>
       </c>
-      <c r="AN197" t="s" s="2">
+      <c r="B205" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="C205" s="2"/>
+      <c r="D205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E205" s="2"/>
+      <c r="F205" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G205" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K205" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L205" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M205" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
+      <c r="P205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q205" s="2"/>
+      <c r="R205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF205" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG205" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH205" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN205" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO205" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP205" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="206" hidden="true">
+      <c r="A206" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="AO197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP197" t="s" s="2">
+      <c r="B206" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C206" s="2"/>
+      <c r="D206" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E206" s="2"/>
+      <c r="F206" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G206" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K206" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L206" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M206" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N206" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O206" s="2"/>
+      <c r="P206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q206" s="2"/>
+      <c r="R206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF206" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG206" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH206" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ206" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN206" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AO206" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP206" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="207" hidden="true">
+      <c r="A207" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E207" s="2"/>
+      <c r="F207" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G207" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I207" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J207" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K207" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L207" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M207" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O207" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q207" s="2"/>
+      <c r="R207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF207" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG207" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH207" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ207" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN207" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP207" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="208" hidden="true">
+      <c r="A208" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C208" s="2"/>
+      <c r="D208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E208" s="2"/>
+      <c r="F208" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G208" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H208" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K208" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="L208" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="M208" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="N208" s="2"/>
+      <c r="O208" s="2"/>
+      <c r="P208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q208" s="2"/>
+      <c r="R208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF208" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="AG208" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH208" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ208" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK208" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AL208" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AM208" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AN208" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AO208" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AP208" t="s" s="2">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="209" hidden="true">
+      <c r="A209" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C209" s="2"/>
+      <c r="D209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E209" s="2"/>
+      <c r="F209" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G209" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K209" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L209" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M209" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="O209" s="2"/>
+      <c r="P209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q209" s="2"/>
+      <c r="R209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X209" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y209" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="Z209" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AA209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF209" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AG209" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH209" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ209" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN209" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AO209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP209" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="210" hidden="true">
+      <c r="A210" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C210" s="2"/>
+      <c r="D210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E210" s="2"/>
+      <c r="F210" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G210" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K210" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L210" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M210" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="O210" s="2"/>
+      <c r="P210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q210" s="2"/>
+      <c r="R210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X210" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="Y210" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="Z210" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AA210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF210" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AG210" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH210" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ210" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP210" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="211" hidden="true">
+      <c r="A211" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C211" s="2"/>
+      <c r="D211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E211" s="2"/>
+      <c r="F211" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G211" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K211" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L211" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M211" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
+      <c r="P211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q211" s="2"/>
+      <c r="R211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF211" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG211" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH211" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ211" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN211" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AO211" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP211" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="212" hidden="true">
+      <c r="A212" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C212" s="2"/>
+      <c r="D212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E212" s="2"/>
+      <c r="F212" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G212" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H212" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K212" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="L212" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="M212" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="N212" s="2"/>
+      <c r="O212" s="2"/>
+      <c r="P212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q212" s="2"/>
+      <c r="R212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF212" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AG212" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH212" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ212" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK212" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="AL212" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AM212" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN212" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="AO212" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP212" t="s" s="2">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="213" hidden="true">
+      <c r="A213" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E213" s="2"/>
+      <c r="F213" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G213" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K213" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="L213" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="M213" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="O213" s="2"/>
+      <c r="P213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q213" s="2"/>
+      <c r="R213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF213" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="AG213" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH213" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ213" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM213" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="AN213" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AO213" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP213" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP197">
+  <autoFilter ref="A1:AP213">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -26477,7 +28456,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI196">
+  <conditionalFormatting sqref="A2:AI212">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8120" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8120" uniqueCount="821">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -892,6 +892,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+EncounterInpatientEncounter-433:if null or &gt; now then fixed value #planned {null}EncounterInpatientEncounter-434:if not null, &lt; now, field 70 null then fixed value #in-progress {null}EncounterInpatientEncounter-435:if not null then fixed value #finished {null}</t>
   </si>
   <si>
     <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) case not null</t>
@@ -8420,33 +8424,33 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>284</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8469,16 +8473,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8528,7 +8532,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8563,10 +8567,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8681,10 +8685,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8801,14 +8805,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8830,10 +8834,10 @@
         <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>139</v>
@@ -8888,7 +8892,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8923,10 +8927,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9006,7 +9010,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>90</v>
@@ -9041,10 +9045,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9070,10 +9074,10 @@
         <v>207</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9124,7 +9128,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>90</v>
@@ -9159,10 +9163,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9188,10 +9192,10 @@
         <v>233</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9203,7 +9207,7 @@
         <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>82</v>
@@ -9221,10 +9225,10 @@
         <v>184</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -9242,7 +9246,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>90</v>
@@ -9257,7 +9261,7 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
@@ -9266,21 +9270,21 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9303,13 +9307,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9360,7 +9364,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9395,10 +9399,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9513,10 +9517,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9633,14 +9637,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9662,10 +9666,10 @@
         <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>139</v>
@@ -9720,7 +9724,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9755,10 +9759,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9784,10 +9788,10 @@
         <v>233</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9817,10 +9821,10 @@
         <v>184</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9838,7 +9842,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>90</v>
@@ -9873,10 +9877,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9902,10 +9906,10 @@
         <v>207</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9956,7 +9960,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>90</v>
@@ -9991,10 +9995,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10020,13 +10024,13 @@
         <v>179</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10055,10 +10059,10 @@
         <v>184</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -10076,7 +10080,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10091,30 +10095,30 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10229,10 +10233,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10349,10 +10353,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10471,10 +10475,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10589,10 +10593,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10709,10 +10713,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10738,16 +10742,16 @@
         <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10757,7 +10761,7 @@
         <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>82</v>
@@ -10796,7 +10800,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10811,7 +10815,7 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
@@ -10820,21 +10824,21 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10860,13 +10864,13 @@
         <v>158</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10916,7 +10920,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10940,21 +10944,21 @@
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10980,14 +10984,14 @@
         <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -11036,7 +11040,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11051,30 +11055,30 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11100,14 +11104,14 @@
         <v>158</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -11156,7 +11160,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11171,30 +11175,30 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11217,19 +11221,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11278,7 +11282,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11302,21 +11306,21 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11415,10 +11419,10 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>82</v>
@@ -11435,10 +11439,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11464,10 +11468,10 @@
         <v>179</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11494,13 +11498,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11518,7 +11522,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11539,7 +11543,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>162</v>
@@ -11548,15 +11552,15 @@
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11582,10 +11586,10 @@
         <v>179</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11612,13 +11616,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11636,7 +11640,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11660,25 +11664,25 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11697,16 +11701,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11756,7 +11760,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11771,30 +11775,30 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11817,13 +11821,13 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11874,7 +11878,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11895,28 +11899,28 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11935,13 +11939,13 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11992,7 +11996,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -12013,10 +12017,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -12027,10 +12031,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12053,13 +12057,13 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12110,7 +12114,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12131,24 +12135,24 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12263,10 +12267,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12383,14 +12387,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12412,10 +12416,10 @@
         <v>136</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>139</v>
@@ -12470,7 +12474,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12505,10 +12509,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12534,13 +12538,13 @@
         <v>179</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12569,10 +12573,10 @@
         <v>184</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12590,7 +12594,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12611,24 +12615,24 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12743,10 +12747,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12863,10 +12867,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12911,7 +12915,7 @@
         <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>82</v>
@@ -12965,7 +12969,7 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>82</v>
@@ -12985,10 +12989,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13107,10 +13111,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13136,10 +13140,10 @@
         <v>207</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13190,7 +13194,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13205,7 +13209,7 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>82</v>
@@ -13214,21 +13218,21 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13251,13 +13255,13 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -13308,7 +13312,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13323,30 +13327,30 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13369,13 +13373,13 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13426,7 +13430,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13447,24 +13451,24 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13490,13 +13494,13 @@
         <v>207</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13546,7 +13550,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13567,24 +13571,24 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13699,10 +13703,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13819,10 +13823,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13845,16 +13849,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13904,7 +13908,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13913,36 +13917,36 @@
         <v>90</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13965,23 +13969,23 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="R93" t="s" s="2">
         <v>82</v>
@@ -14026,7 +14030,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14035,36 +14039,36 @@
         <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14087,16 +14091,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14146,7 +14150,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14167,28 +14171,28 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -14210,13 +14214,13 @@
         <v>179</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14245,10 +14249,10 @@
         <v>114</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -14264,7 +14268,7 @@
         <v>152</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14285,30 +14289,30 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14330,13 +14334,13 @@
         <v>179</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14365,10 +14369,10 @@
         <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14386,7 +14390,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14407,24 +14411,24 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14539,10 +14543,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14659,10 +14663,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14781,10 +14785,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14899,10 +14903,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15019,10 +15023,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15048,16 +15052,16 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -15067,7 +15071,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -15106,7 +15110,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15121,7 +15125,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -15130,21 +15134,21 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15170,13 +15174,13 @@
         <v>158</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15226,7 +15230,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15250,21 +15254,21 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15290,14 +15294,14 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15346,7 +15350,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15361,30 +15365,30 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15410,14 +15414,14 @@
         <v>158</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15466,7 +15470,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15490,21 +15494,21 @@
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15527,19 +15531,19 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15588,7 +15592,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15612,21 +15616,21 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15745,16 +15749,16 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15776,13 +15780,13 @@
         <v>179</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15811,10 +15815,10 @@
         <v>114</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15832,7 +15836,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15853,24 +15857,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15985,10 +15989,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16105,10 +16109,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16227,10 +16231,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16345,10 +16349,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16465,10 +16469,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16494,16 +16498,16 @@
         <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16513,7 +16517,7 @@
         <v>82</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>82</v>
@@ -16552,7 +16556,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16567,7 +16571,7 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
@@ -16576,21 +16580,21 @@
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16616,13 +16620,13 @@
         <v>158</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16672,7 +16676,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16696,21 +16700,21 @@
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16736,14 +16740,14 @@
         <v>110</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16792,7 +16796,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16807,30 +16811,30 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16856,14 +16860,14 @@
         <v>158</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16912,7 +16916,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16936,21 +16940,21 @@
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16973,19 +16977,19 @@
         <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -17034,7 +17038,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -17058,21 +17062,21 @@
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17191,16 +17195,16 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17222,13 +17226,13 @@
         <v>179</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17257,10 +17261,10 @@
         <v>114</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>82</v>
@@ -17278,7 +17282,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17299,24 +17303,24 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17431,10 +17435,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17551,10 +17555,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17673,10 +17677,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17791,10 +17795,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17911,10 +17915,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17940,16 +17944,16 @@
         <v>104</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17959,7 +17963,7 @@
         <v>82</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>82</v>
@@ -17998,7 +18002,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -18013,7 +18017,7 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>82</v>
@@ -18022,21 +18026,21 @@
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18062,13 +18066,13 @@
         <v>158</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -18118,7 +18122,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18142,21 +18146,21 @@
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18182,14 +18186,14 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -18238,7 +18242,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18253,30 +18257,30 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18302,14 +18306,14 @@
         <v>158</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
@@ -18358,7 +18362,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18382,21 +18386,21 @@
         <v>82</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18419,19 +18423,19 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18480,7 +18484,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18504,21 +18508,21 @@
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18637,14 +18641,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -18663,16 +18667,16 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18722,7 +18726,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18743,24 +18747,24 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18783,13 +18787,13 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18840,7 +18844,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18864,7 +18868,7 @@
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18875,10 +18879,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18993,10 +18997,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19113,14 +19117,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -19142,10 +19146,10 @@
         <v>136</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>139</v>
@@ -19200,7 +19204,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19235,14 +19239,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -19261,16 +19265,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19320,7 +19324,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>90</v>
@@ -19335,30 +19339,30 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19384,10 +19388,10 @@
         <v>179</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19417,10 +19421,10 @@
         <v>114</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -19438,7 +19442,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19473,10 +19477,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19499,13 +19503,13 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19556,7 +19560,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19571,7 +19575,7 @@
         <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>82</v>
@@ -19580,7 +19584,7 @@
         <v>82</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
@@ -19591,10 +19595,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19617,16 +19621,16 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19676,7 +19680,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19700,7 +19704,7 @@
         <v>82</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
@@ -19711,10 +19715,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19737,16 +19741,16 @@
         <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19796,7 +19800,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19820,7 +19824,7 @@
         <v>82</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19831,10 +19835,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19949,10 +19953,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20069,14 +20073,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -20098,10 +20102,10 @@
         <v>136</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>139</v>
@@ -20156,7 +20160,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20191,10 +20195,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20220,10 +20224,10 @@
         <v>148</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20274,7 +20278,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20304,15 +20308,15 @@
         <v>82</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20335,13 +20339,13 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20392,7 +20396,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20416,7 +20420,7 @@
         <v>82</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20427,10 +20431,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20545,10 +20549,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20665,10 +20669,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20694,13 +20698,13 @@
         <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20750,7 +20754,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20759,7 +20763,7 @@
         <v>90</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>102</v>
@@ -20785,10 +20789,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20814,13 +20818,13 @@
         <v>104</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20849,10 +20853,10 @@
         <v>184</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20870,7 +20874,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20905,10 +20909,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20934,13 +20938,13 @@
         <v>148</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20990,7 +20994,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -21014,7 +21018,7 @@
         <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
@@ -21025,10 +21029,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21054,13 +21058,13 @@
         <v>158</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21110,7 +21114,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21125,10 +21129,10 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>82</v>
@@ -21145,10 +21149,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21174,10 +21178,10 @@
         <v>179</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21207,10 +21211,10 @@
         <v>114</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>82</v>
@@ -21228,7 +21232,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21252,21 +21256,21 @@
         <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21381,10 +21385,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21501,10 +21505,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21568,7 +21572,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21601,10 +21605,10 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
@@ -21621,10 +21625,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21739,10 +21743,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21859,10 +21863,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21888,16 +21892,16 @@
         <v>104</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -21907,7 +21911,7 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>82</v>
@@ -21946,7 +21950,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21961,7 +21965,7 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -21970,21 +21974,21 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22010,13 +22014,13 @@
         <v>158</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -22066,7 +22070,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22090,21 +22094,21 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22130,14 +22134,14 @@
         <v>110</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -22186,7 +22190,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -22201,30 +22205,30 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22250,14 +22254,14 @@
         <v>158</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -22306,7 +22310,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22330,21 +22334,21 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22367,19 +22371,19 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22428,7 +22432,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22452,21 +22456,21 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22585,10 +22589,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22614,10 +22618,10 @@
         <v>179</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22644,13 +22648,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22668,7 +22672,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22698,15 +22702,15 @@
         <v>82</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22732,16 +22736,16 @@
         <v>179</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22766,13 +22770,13 @@
         <v>82</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22790,7 +22794,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22814,21 +22818,21 @@
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22854,10 +22858,10 @@
         <v>179</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22887,10 +22891,10 @@
         <v>114</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22908,7 +22912,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22932,21 +22936,21 @@
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22972,10 +22976,10 @@
         <v>179</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -23005,10 +23009,10 @@
         <v>114</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -23026,7 +23030,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23050,21 +23054,21 @@
         <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23087,13 +23091,13 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23144,7 +23148,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23168,21 +23172,21 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23297,10 +23301,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23417,10 +23421,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23446,13 +23450,13 @@
         <v>158</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23502,7 +23506,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23511,7 +23515,7 @@
         <v>90</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>102</v>
@@ -23537,10 +23541,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23566,13 +23570,13 @@
         <v>104</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23601,10 +23605,10 @@
         <v>184</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -23622,7 +23626,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23657,10 +23661,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23686,13 +23690,13 @@
         <v>148</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23742,7 +23746,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23766,7 +23770,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23777,10 +23781,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23806,13 +23810,13 @@
         <v>158</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23862,7 +23866,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23877,10 +23881,10 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>82</v>
@@ -23897,10 +23901,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23926,10 +23930,10 @@
         <v>179</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23959,10 +23963,10 @@
         <v>114</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
@@ -23980,7 +23984,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24004,21 +24008,21 @@
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24133,10 +24137,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24253,10 +24257,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24375,10 +24379,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24493,10 +24497,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24613,10 +24617,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24642,16 +24646,16 @@
         <v>104</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24661,7 +24665,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24700,7 +24704,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24715,7 +24719,7 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>82</v>
@@ -24724,21 +24728,21 @@
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24764,13 +24768,13 @@
         <v>158</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -24820,7 +24824,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24844,21 +24848,21 @@
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24884,14 +24888,14 @@
         <v>110</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -24940,7 +24944,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -24955,30 +24959,30 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25004,14 +25008,14 @@
         <v>158</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -25060,7 +25064,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -25084,21 +25088,21 @@
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25121,19 +25125,19 @@
         <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>82</v>
@@ -25182,7 +25186,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25206,21 +25210,21 @@
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP186" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25339,10 +25343,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25365,16 +25369,16 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25422,7 +25426,7 @@
         <v>152</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25446,7 +25450,7 @@
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
@@ -25457,10 +25461,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25575,10 +25579,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25695,14 +25699,14 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
@@ -25724,10 +25728,10 @@
         <v>136</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N191" t="s" s="2">
         <v>139</v>
@@ -25782,7 +25786,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25817,10 +25821,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25843,13 +25847,13 @@
         <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25900,7 +25904,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>90</v>
@@ -25921,24 +25925,24 @@
         <v>82</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25964,13 +25968,13 @@
         <v>110</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25999,10 +26003,10 @@
         <v>173</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -26020,7 +26024,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -26044,7 +26048,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -26055,10 +26059,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26084,13 +26088,13 @@
         <v>179</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26116,13 +26120,13 @@
         <v>82</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -26140,7 +26144,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26175,10 +26179,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26204,10 +26208,10 @@
         <v>207</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26258,7 +26262,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26282,7 +26286,7 @@
         <v>82</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>82</v>
@@ -26293,13 +26297,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>82</v>
@@ -26321,16 +26325,16 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26380,7 +26384,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26404,7 +26408,7 @@
         <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
@@ -26415,10 +26419,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26533,10 +26537,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26653,14 +26657,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -26682,10 +26686,10 @@
         <v>136</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N199" t="s" s="2">
         <v>139</v>
@@ -26740,7 +26744,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -26775,10 +26779,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26801,13 +26805,13 @@
         <v>82</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -26858,7 +26862,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>90</v>
@@ -26873,30 +26877,30 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AP200" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26922,13 +26926,13 @@
         <v>110</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -26957,10 +26961,10 @@
         <v>173</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>82</v>
@@ -26978,7 +26982,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -27002,7 +27006,7 @@
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>82</v>
@@ -27013,10 +27017,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27042,13 +27046,13 @@
         <v>179</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -27074,13 +27078,13 @@
         <v>82</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>82</v>
@@ -27098,7 +27102,7 @@
         <v>82</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -27133,10 +27137,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27162,10 +27166,10 @@
         <v>207</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -27216,7 +27220,7 @@
         <v>82</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -27240,7 +27244,7 @@
         <v>82</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>82</v>
@@ -27251,13 +27255,13 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D204" t="s" s="2">
         <v>82</v>
@@ -27279,16 +27283,16 @@
         <v>82</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -27338,7 +27342,7 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -27362,7 +27366,7 @@
         <v>82</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>82</v>
@@ -27373,10 +27377,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27491,10 +27495,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27611,14 +27615,14 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
@@ -27640,10 +27644,10 @@
         <v>136</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N207" t="s" s="2">
         <v>139</v>
@@ -27698,7 +27702,7 @@
         <v>82</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27733,10 +27737,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27759,13 +27763,13 @@
         <v>82</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -27816,7 +27820,7 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>90</v>
@@ -27831,30 +27835,30 @@
         <v>102</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AP208" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27880,13 +27884,13 @@
         <v>110</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -27915,10 +27919,10 @@
         <v>173</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>82</v>
@@ -27936,7 +27940,7 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -27960,7 +27964,7 @@
         <v>82</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>82</v>
@@ -27971,10 +27975,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28000,13 +28004,13 @@
         <v>179</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28032,13 +28036,13 @@
         <v>82</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>82</v>
@@ -28056,7 +28060,7 @@
         <v>82</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -28091,10 +28095,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28120,10 +28124,10 @@
         <v>207</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -28174,7 +28178,7 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28198,7 +28202,7 @@
         <v>82</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>82</v>
@@ -28209,10 +28213,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28235,13 +28239,13 @@
         <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -28292,7 +28296,7 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28307,30 +28311,30 @@
         <v>102</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP212" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28353,16 +28357,16 @@
         <v>82</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -28412,7 +28416,7 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28433,10 +28437,10 @@
         <v>82</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -895,7 +895,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-EncounterInpatientEncounter-433:if null or &gt; now then fixed value #planned {null}EncounterInpatientEncounter-434:if not null, &lt; now, field 70 null then fixed value #in-progress {null}EncounterInpatientEncounter-435:if not null then fixed value #finished {null}</t>
+eie-27-433:45-2: if null or &gt; now then #planned {null}eie-27-434:45-2: if not null, &lt; now, field 70 null then #in-progress {null}eie-27-435:45-70: if not null then #finished {null}</t>
   </si>
   <si>
     <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) case not null</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1299,7 +1299,7 @@
     <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census501.PatientSID,Inpat.Census535.PatientIEN,Inpat.CensusDiagnosis.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientFeeDiagnosis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
   </si>
   <si>
-    <t>Diagnosis.CodeTableDetail.Diagnosis.Code</t>
+    <t>Diagnosis.Diagnosis[CodeTableDetail.Diagnosis].Code</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PTF (45) to us-core-encounter</t>
+    <t>This StructureDefinition contains the maps for VistA file PTF (45) to us-core-encounter.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8333" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8333" uniqueCount="829">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,7 +491,7 @@
     <t>Identifier(s) by which this encounter is known.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -1844,6 +1844,9 @@
   </si>
   <si>
     <t>Reason the encounter takes place (reference)</t>
+  </si>
+  <si>
+    <t>2144: target not supported</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -19156,7 +19159,7 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>83</v>
+        <v>593</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>83</v>
@@ -19179,10 +19182,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19208,10 +19211,10 @@
         <v>294</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -19262,7 +19265,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19289,7 +19292,7 @@
         <v>83</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>
@@ -19300,10 +19303,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19421,10 +19424,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19544,10 +19547,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19669,14 +19672,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -19695,13 +19698,13 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>521</v>
@@ -19754,7 +19757,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>91</v>
@@ -19769,7 +19772,7 @@
         <v>103</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>83</v>
@@ -19778,24 +19781,24 @@
         <v>83</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>526</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19821,10 +19824,10 @@
         <v>180</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19854,10 +19857,10 @@
         <v>115</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>83</v>
@@ -19875,7 +19878,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19913,10 +19916,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19939,13 +19942,13 @@
         <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19996,7 +19999,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -20011,7 +20014,7 @@
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>83</v>
@@ -20023,7 +20026,7 @@
         <v>83</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>83</v>
@@ -20034,10 +20037,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20060,16 +20063,16 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -20119,7 +20122,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -20146,7 +20149,7 @@
         <v>83</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP140" t="s" s="2">
         <v>83</v>
@@ -20157,10 +20160,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20186,13 +20189,13 @@
         <v>294</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20242,7 +20245,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -20269,7 +20272,7 @@
         <v>83</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP141" t="s" s="2">
         <v>83</v>
@@ -20280,10 +20283,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20401,10 +20404,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20524,10 +20527,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20649,10 +20652,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20678,10 +20681,10 @@
         <v>149</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20732,7 +20735,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20765,15 +20768,15 @@
         <v>83</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20796,13 +20799,13 @@
         <v>83</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20853,7 +20856,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20880,7 +20883,7 @@
         <v>83</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP146" t="s" s="2">
         <v>83</v>
@@ -20891,10 +20894,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21012,10 +21015,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21135,10 +21138,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21164,13 +21167,13 @@
         <v>159</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -21220,7 +21223,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -21229,7 +21232,7 @@
         <v>91</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>103</v>
@@ -21258,10 +21261,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21287,13 +21290,13 @@
         <v>105</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -21322,10 +21325,10 @@
         <v>185</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>83</v>
@@ -21343,7 +21346,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -21381,10 +21384,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21410,13 +21413,13 @@
         <v>149</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -21466,7 +21469,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -21493,7 +21496,7 @@
         <v>83</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>83</v>
@@ -21504,10 +21507,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21533,13 +21536,13 @@
         <v>159</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21589,7 +21592,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21604,10 +21607,10 @@
         <v>103</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>83</v>
@@ -21627,10 +21630,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21656,10 +21659,10 @@
         <v>180</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21689,10 +21692,10 @@
         <v>115</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>83</v>
@@ -21710,7 +21713,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21737,21 +21740,21 @@
         <v>83</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP153" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21869,10 +21872,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21992,10 +21995,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22059,7 +22062,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>83</v>
@@ -22092,10 +22095,10 @@
         <v>103</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>83</v>
@@ -22115,10 +22118,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22236,10 +22239,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22359,10 +22362,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22407,7 +22410,7 @@
         <v>83</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>83</v>
@@ -22461,7 +22464,7 @@
         <v>103</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>83</v>
@@ -22484,10 +22487,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22607,10 +22610,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22707,10 +22710,10 @@
         <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>83</v>
@@ -22730,10 +22733,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22853,10 +22856,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22978,10 +22981,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23103,10 +23106,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23132,10 +23135,10 @@
         <v>180</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -23165,10 +23168,10 @@
         <v>396</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
@@ -23186,7 +23189,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23219,15 +23222,15 @@
         <v>83</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23253,16 +23256,16 @@
         <v>180</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>83</v>
@@ -23290,10 +23293,10 @@
         <v>396</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>83</v>
@@ -23311,7 +23314,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23338,21 +23341,21 @@
         <v>83</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23378,10 +23381,10 @@
         <v>180</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -23411,10 +23414,10 @@
         <v>115</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>83</v>
@@ -23432,7 +23435,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23459,21 +23462,21 @@
         <v>83</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23499,10 +23502,10 @@
         <v>180</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -23532,10 +23535,10 @@
         <v>115</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>83</v>
@@ -23553,7 +23556,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23580,21 +23583,21 @@
         <v>83</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AP168" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23617,13 +23620,13 @@
         <v>83</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23674,7 +23677,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -23701,21 +23704,21 @@
         <v>83</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AP169" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ169" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23833,10 +23836,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23956,10 +23959,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23985,13 +23988,13 @@
         <v>159</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -24041,7 +24044,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -24050,7 +24053,7 @@
         <v>91</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>103</v>
@@ -24079,10 +24082,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24108,13 +24111,13 @@
         <v>105</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -24143,10 +24146,10 @@
         <v>185</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>83</v>
@@ -24164,7 +24167,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24202,10 +24205,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24231,13 +24234,13 @@
         <v>149</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -24287,7 +24290,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24314,7 +24317,7 @@
         <v>83</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AP174" t="s" s="2">
         <v>83</v>
@@ -24325,10 +24328,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24354,13 +24357,13 @@
         <v>159</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -24410,7 +24413,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24425,10 +24428,10 @@
         <v>103</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>83</v>
@@ -24448,10 +24451,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24477,10 +24480,10 @@
         <v>180</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24510,10 +24513,10 @@
         <v>115</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>83</v>
@@ -24531,7 +24534,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -24558,21 +24561,21 @@
         <v>83</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ176" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24690,10 +24693,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24813,10 +24816,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24938,10 +24941,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25059,10 +25062,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25182,10 +25185,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25230,7 +25233,7 @@
         <v>83</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>83</v>
@@ -25284,7 +25287,7 @@
         <v>103</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>83</v>
@@ -25307,10 +25310,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25430,10 +25433,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25530,10 +25533,10 @@
         <v>103</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>83</v>
@@ -25553,10 +25556,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25676,10 +25679,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25801,10 +25804,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25926,10 +25929,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25955,13 +25958,13 @@
         <v>294</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -26009,7 +26012,7 @@
         <v>153</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -26036,7 +26039,7 @@
         <v>83</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>83</v>
@@ -26047,10 +26050,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26168,10 +26171,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26291,10 +26294,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26416,10 +26419,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26442,13 +26445,13 @@
         <v>83</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -26499,7 +26502,7 @@
         <v>83</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>91</v>
@@ -26523,24 +26526,24 @@
         <v>83</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>470</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26566,13 +26569,13 @@
         <v>111</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26601,10 +26604,10 @@
         <v>174</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -26622,7 +26625,7 @@
         <v>83</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -26649,7 +26652,7 @@
         <v>83</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AP193" t="s" s="2">
         <v>83</v>
@@ -26660,10 +26663,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26689,13 +26692,13 @@
         <v>180</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26724,10 +26727,10 @@
         <v>396</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>83</v>
@@ -26745,7 +26748,7 @@
         <v>83</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -26783,10 +26786,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26812,10 +26815,10 @@
         <v>208</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26866,7 +26869,7 @@
         <v>83</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -26904,13 +26907,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>83</v>
@@ -26935,13 +26938,13 @@
         <v>294</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26991,7 +26994,7 @@
         <v>83</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -27018,7 +27021,7 @@
         <v>83</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>83</v>
@@ -27029,10 +27032,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27150,10 +27153,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27273,10 +27276,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -27398,10 +27401,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27424,13 +27427,13 @@
         <v>83</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -27481,7 +27484,7 @@
         <v>83</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>91</v>
@@ -27496,33 +27499,33 @@
         <v>103</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>470</v>
       </c>
       <c r="AP200" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AQ200" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27548,13 +27551,13 @@
         <v>111</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -27583,10 +27586,10 @@
         <v>174</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>83</v>
@@ -27604,7 +27607,7 @@
         <v>83</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -27631,7 +27634,7 @@
         <v>83</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>83</v>
@@ -27642,10 +27645,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27671,13 +27674,13 @@
         <v>180</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -27706,10 +27709,10 @@
         <v>396</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>83</v>
@@ -27727,7 +27730,7 @@
         <v>83</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27765,10 +27768,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27794,10 +27797,10 @@
         <v>208</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -27848,7 +27851,7 @@
         <v>83</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27886,13 +27889,13 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D204" t="s" s="2">
         <v>83</v>
@@ -27917,13 +27920,13 @@
         <v>294</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -27973,7 +27976,7 @@
         <v>83</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -28000,7 +28003,7 @@
         <v>83</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>83</v>
@@ -28011,10 +28014,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28132,10 +28135,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28255,10 +28258,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28380,10 +28383,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28406,13 +28409,13 @@
         <v>83</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -28463,7 +28466,7 @@
         <v>83</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>91</v>
@@ -28478,33 +28481,33 @@
         <v>103</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>470</v>
       </c>
       <c r="AP208" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AQ208" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28530,13 +28533,13 @@
         <v>111</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -28565,10 +28568,10 @@
         <v>174</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>83</v>
@@ -28586,7 +28589,7 @@
         <v>83</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28613,7 +28616,7 @@
         <v>83</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>83</v>
@@ -28624,10 +28627,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28653,13 +28656,13 @@
         <v>180</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28688,10 +28691,10 @@
         <v>396</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>83</v>
@@ -28709,7 +28712,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -28747,10 +28750,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28776,10 +28779,10 @@
         <v>208</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -28830,7 +28833,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28868,10 +28871,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28894,13 +28897,13 @@
         <v>83</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -28951,7 +28954,7 @@
         <v>83</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -28966,33 +28969,33 @@
         <v>103</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>469</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ212" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29015,16 +29018,16 @@
         <v>83</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -29074,7 +29077,7 @@
         <v>83</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -29098,10 +29101,10 @@
         <v>83</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -813,7 +813,7 @@
     <t>Encounter.identifier:va-IEN.value</t>
   </si>
   <si>
-    <t>427: source value from PTF - NUMBER (45-.001)</t>
+    <t>427: source value based on PTF - NUMBER (45-.001)</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IEN.period</t>
@@ -870,7 +870,7 @@
     <t>Encounter.identifier:va-IA.value</t>
   </si>
   <si>
-    <t>428: source value from PTF - INTERNAL ADMISSION # (45-2.1)</t>
+    <t>428: source value based on PTF - INTERNAL ADMISSION # (45-2.1)</t>
   </si>
   <si>
     <t>Encounter.identifier:va-IA.period</t>
@@ -898,10 +898,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-eie-27-433:45-2: if null or &gt; now then #planned {null}eie-27-434:45-2: if not null, &lt; now, field 70 null then #in-progress {null}eie-27-435:45-70: if not null then #finished {null}</t>
-  </si>
-  <si>
-    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) case not null</t>
+eie-27-433:If (45-2) is null or &gt; now then fixed value #planned {null}eie-27-434:If (45-2) is not null, &lt; now, field 70 null then fixed value #in-progress {null}eie-27-435:If (45-70) is not null then fixed value #finished {null}</t>
+  </si>
+  <si>
+    <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) if not null</t>
   </si>
   <si>
     <t>Inpat.Census.CensusDateSID,Inpat.Census.CensusDateTime,Inpat.Census501.CensusDateTime,Inpat.Census501Diagnosis.CensusDateTime,Inpat.Census535.CensusDateTime,Inpat.CensusDiagnosis.CensusDateTime,Inpat.CensusICDProcedure.CensusDateTime,Inpat.CensusSurgicalProcedure.CensusDateTime,Inpat.Inpatient.DischargeDateTime,Inpat.Inpatient501Transaction.DischargeDateTime,Inpat.Inpatient501TransactionDiagnosis.DischargeDateTime,Inpat.Inpatient535Multiple.DischargeDateTime,Inpat.Inpatient535Transaction.DischargeDateTime,Inpat.InpatientDiagnosis.DischargeDateTime,Inpat.InpatientFeeBasis.DischargeDateTime,Inpat.InpatientFeeDiagnosis.DischargeDateTime,Inpat.InpatientICDProcedure.DischargeDateTime,Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
@@ -1060,7 +1060,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-encounter-type</t>
   </si>
   <si>
-    <t>1616: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT (46-.01 &gt; 81-)</t>
+    <t>1616: source value based on INPATIENT CPT CODE - CPT CODE &gt; CPT (46-.01 &gt; 81-)</t>
   </si>
   <si>
     <t>Inpat.InpatientCPTProcedure.CPTIEN</t>
@@ -1156,7 +1156,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1616-2: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT - CPT CODE (46-.01 &gt; 81-.01)</t>
+    <t>1616-2: source value based on INPATIENT CPT CODE - CPT CODE &gt; CPT - CPT CODE (46-.01 &gt; 81-.01)</t>
   </si>
   <si>
     <t>Inpat.InpatientCPTProcedure.CPTIEN
@@ -1184,7 +1184,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1616-3: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT - SHORT NAME (46-.01 &gt; 81-2)</t>
+    <t>1616-3: source value based on INPATIENT CPT CODE - CPT CODE &gt; CPT - SHORT NAME (46-.01 &gt; 81-2)</t>
   </si>
   <si>
     <t>Inpat.InpatientCPTProcedure.CPTIEN
@@ -1228,7 +1228,7 @@
     <t>Encounter.type.text</t>
   </si>
   <si>
-    <t>1616-4: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT - SHORT NAME (46-.01 &gt; 81-2)</t>
+    <t>1616-4: source value based on INPATIENT CPT CODE - CPT CODE &gt; CPT - SHORT NAME (46-.01 &gt; 81-2)</t>
   </si>
   <si>
     <t>Encounter.serviceType</t>
@@ -1293,7 +1293,7 @@
     <t>While the encounter is always about the patient, the patient might not actually be known in all contexts of use, and there may be a group of patients that could be anonymous (such as in a group therapy for Alcoholics Anonymous - where the recording of the encounter could be used for billing on the number of people/staff and not important to the context of the specific patients) or alternately in veterinary care a herd of sheep receiving treatment (where the animals are not individually tracked).</t>
   </si>
   <si>
-    <t>441: reference from PTF - PATIENT (45-.01)</t>
+    <t>441: reference based on PTF - PATIENT (45-.01)</t>
   </si>
   <si>
     <t>Inpat.Census.PatientIEN,Inpat.Census501.PatientIEN,Inpat.Census501.PatientSID,Inpat.Census535.PatientIEN,Inpat.CensusDiagnosis.PatientIEN,Inpat.CensusICDProcedure.PatientIEN,Inpat.CensusSurgicalProcedure.PatientIEN,Inpat.Inpatient.PatientIEN,Inpat.Inpatient501Transaction.PatientIEN,Inpat.Inpatient535Transaction.PatientIEN,Inpat.InpatientDiagnosis.PatientIEN,Inpat.InpatientDischargeDiagnosis.PatientIEN,Inpat.InpatientFeeBasis.PatientIEN,Inpat.InpatientFeeDiagnosis.PatientIEN,Inpat.InpatientICDProcedure.PatientIEN,Inpat.InpatientSurgicalProcedure.PatientIEN,Inpat.PresentOnAdmission.PatientIEN</t>
@@ -1462,7 +1462,7 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
-    <t>442: reference from PTF - PROVIDER (45-79.1)</t>
+    <t>442: reference based on PTF - PROVIDER (45-79.1)</t>
   </si>
   <si>
     <t>Diagnosis.DiagnosingClinician</t>
@@ -1552,7 +1552,7 @@
 </t>
   </si>
   <si>
-    <t>445: source value from PTF - ADMISSION DATE (45-2)</t>
+    <t>445: source value based on PTF - ADMISSION DATE (45-2)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitDateSID,Inpat.Census.AdmitDateTime,Inpat.Census501.AdmitDateTime,Inpat.Census501Diagnosis.AdmitDateTime,Inpat.Census535.AdmitDateTime,Inpat.CensusDiagnosis.AdmitDateTime,Inpat.CensusICDProcedure.AdmitDateTime,Inpat.CensusSurgicalProcedure.AdmitDateTime,Inpat.Inpatient.AdmitDateTime,Inpat.Inpatient501Multiple.AdmitDateTime,Inpat.Inpatient501Transaction.AdmitDateTime,Inpat.Inpatient535Multiple.AdmitDateTime,Inpat.Inpatient535Transaction.AdmitDateTime,Inpat.InpatientDischargeDiagnosis.AdmitDateTime,Inpat.InpatientFeeBasis.AdmitDateTime,Inpat.InpatientFeeDiagnosis.AdmitDateTime,Inpat.InpatientICDProcedure.AdmitDateTime,Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
@@ -1585,7 +1585,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>446: source value from PTF - DISCHARGE DATE (45-70)</t>
+    <t>446: source value based on PTF - DISCHARGE DATE (45-70)</t>
   </si>
   <si>
     <t>./high</t>
@@ -1710,7 +1710,7 @@
     <t>Encounter.reasonCode.coding.code</t>
   </si>
   <si>
-    <t>448: source value from PTF - PRINCIPAL DIAGNOSIS (45-79)</t>
+    <t>448: source value based on PTF - PRINCIPAL DIAGNOSIS (45-79)</t>
   </si>
   <si>
     <t>Inpat.Inpatient.PrincipalDiagnosisICDIEN</t>
@@ -1770,7 +1770,7 @@
     <t>Encounter.reasonCode:va-secondary.coding.code</t>
   </si>
   <si>
-    <t>449: source value from PTF - SECONDARY DIAGNOSIS 1-24 &gt; ICD DIAGNOSIS - CODE NUMBER (45-79.* &gt; 80-.01)</t>
+    <t>449: source value based on PTF - SECONDARY DIAGNOSIS 1-24 &gt; ICD DIAGNOSIS - CODE NUMBER (45-79.* &gt; 80-.01)</t>
   </si>
   <si>
     <t>Dim.ICD10.ICD10Code,Dim.ICD9.ICD9Code</t>
@@ -1821,7 +1821,7 @@
     <t>Encounter.reasonCode:va-procedure.coding.code</t>
   </si>
   <si>
-    <t>450: source value from PTF - PROCEDURE 1-5 &gt; ICD OPERATION/PROCEDURE - CODE NUMBER (45-45.01+to+45.05 &gt; 80.1-.01)</t>
+    <t>450: source value based on PTF - PROCEDURE 1-5 &gt; ICD OPERATION/PROCEDURE - CODE NUMBER (45-45.01+to+45.05 &gt; 80.1-.01)</t>
   </si>
   <si>
     <t>Dim.ICD10Procedure.ICD10ProcedureCode,Dim.ICD9Procedure.ICD9ProcedureCode</t>
@@ -2089,7 +2089,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>454: source value from PTF - TRANSFERRING FACILITY (45-21.1)</t>
+    <t>454: source value based on PTF - TRANSFERRING FACILITY (45-21.1)</t>
   </si>
   <si>
     <t>Inpat.Census.TransferringFacility,Inpat.Inpatient.TransferFromFacility,Inpat.InpatientFeeBasis.TransferringFacility</t>
@@ -2156,7 +2156,7 @@
     <t>Encounter.hospitalization.admitSource.coding.code</t>
   </si>
   <si>
-    <t>453: source value from PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
+    <t>453: source value based on PTF - SOURCE OF ADMISSION &gt; SOURCE OF ADMISSION - PTF CODE (45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>Encounter.hospitalization.admitSource.coding.display</t>
@@ -2288,7 +2288,7 @@
     <t>Encounter.hospitalization.destination.display</t>
   </si>
   <si>
-    <t>455: source value from PTF - RECEIVING FACILITY (45-76.1)</t>
+    <t>455: source value based on PTF - RECEIVING FACILITY (45-76.1)</t>
   </si>
   <si>
     <t>Inpat.Census.ReceivingFacility,Inpat.Inpatient.TransferToFacility,Inpat.InpatientFeeBasis.ReceivingFacility</t>
@@ -2345,7 +2345,7 @@
     <t>Encounter.hospitalization.dischargeDisposition.coding.code</t>
   </si>
   <si>
-    <t>456: source value from PTF - PLACE OF DISPOSITION (45-75)</t>
+    <t>456: source value based on PTF - PLACE OF DISPOSITION (45-75)</t>
   </si>
   <si>
     <t>Inpat.Census.PlaceOfDispositionIEN,Inpat.Inpatient.PlaceOfDispositionIEN,Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
@@ -2477,7 +2477,7 @@
 </t>
   </si>
   <si>
-    <t>460: reference from PTF - WARD AT DISCHARGE &gt; WARD LOCATION - HOSPITAL LOCATION FILE POINTER (45-2.2 &gt; 42-44)</t>
+    <t>460: reference based on PTF - WARD AT DISCHARGE &gt; WARD LOCATION - HOSPITAL LOCATION FILE POINTER (45-2.2 &gt; 42-44)</t>
   </si>
   <si>
     <t>Inpat.Inpatient.Discharge45WardLocationIEN
@@ -2511,7 +2511,7 @@
     <t>Encounter.location:va-facility.location</t>
   </si>
   <si>
-    <t>461: reference from PTF - FACILITY (45-3)</t>
+    <t>461: reference based on PTF - FACILITY (45-3)</t>
   </si>
   <si>
     <t>Inpat.Census.DischargeFacility,Inpat.Inpatient.DischargeFromFacility,Inpat.InpatientFeeBasis.DischargeFacility</t>
@@ -2542,7 +2542,7 @@
     <t>The organization that is primarily responsible for this Encounter's services. This MAY be the same as the organization on the Patient record, however it could be different, such as if the actor performing the services was from an external organization (which may be billed seperately) for an external consultation.  Refer to the example bundle showing an abbreviated set of Encounters for a colonoscopy.</t>
   </si>
   <si>
-    <t>1600: reference from PTF - FACILITY (45-3)</t>
+    <t>1600: reference based on PTF - FACILITY (45-3)</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8333" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8334" uniqueCount="830">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2123,6 +2123,9 @@
   </si>
   <si>
     <t>Encounter.hospitalization.admitSource.coding</t>
+  </si>
+  <si>
+    <t>see mapping [VF_SourceOfAdmission](ConceptMap-VF-SourceOfAdmission.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/SourceOfAdmission</t>
@@ -22060,9 +22063,11 @@
       <c r="X156" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y156" s="2"/>
+      <c r="Y156" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="Z156" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>83</v>
@@ -22095,10 +22100,10 @@
         <v>103</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>83</v>
@@ -22118,10 +22123,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22239,10 +22244,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22362,10 +22367,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22410,7 +22415,7 @@
         <v>83</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>83</v>
@@ -22464,7 +22469,7 @@
         <v>103</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>83</v>
@@ -22487,10 +22492,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22610,10 +22615,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22710,10 +22715,10 @@
         <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>83</v>
@@ -22733,10 +22738,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22856,10 +22861,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22981,10 +22986,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23106,10 +23111,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23135,10 +23140,10 @@
         <v>180</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -23168,10 +23173,10 @@
         <v>396</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
@@ -23189,7 +23194,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23222,15 +23227,15 @@
         <v>83</v>
       </c>
       <c r="AQ165" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23256,16 +23261,16 @@
         <v>180</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>83</v>
@@ -23293,10 +23298,10 @@
         <v>396</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>83</v>
@@ -23314,7 +23319,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23341,21 +23346,21 @@
         <v>83</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23381,10 +23386,10 @@
         <v>180</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -23414,10 +23419,10 @@
         <v>115</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>83</v>
@@ -23435,7 +23440,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23462,21 +23467,21 @@
         <v>83</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23502,10 +23507,10 @@
         <v>180</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -23535,10 +23540,10 @@
         <v>115</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>83</v>
@@ -23556,7 +23561,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23583,21 +23588,21 @@
         <v>83</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AP168" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23623,10 +23628,10 @@
         <v>640</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23677,7 +23682,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -23704,21 +23709,21 @@
         <v>83</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP169" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ169" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23836,10 +23841,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23959,10 +23964,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24082,10 +24087,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24205,10 +24210,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24328,10 +24333,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24428,10 +24433,10 @@
         <v>103</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>83</v>
@@ -24451,10 +24456,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24480,10 +24485,10 @@
         <v>180</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24513,10 +24518,10 @@
         <v>115</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>83</v>
@@ -24534,7 +24539,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -24561,21 +24566,21 @@
         <v>83</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ176" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24693,10 +24698,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24816,10 +24821,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24941,10 +24946,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25062,10 +25067,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25185,10 +25190,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25233,7 +25238,7 @@
         <v>83</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>83</v>
@@ -25287,7 +25292,7 @@
         <v>103</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>83</v>
@@ -25310,10 +25315,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25433,10 +25438,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25533,10 +25538,10 @@
         <v>103</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>83</v>
@@ -25556,10 +25561,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25679,10 +25684,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25804,10 +25809,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25929,10 +25934,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25958,13 +25963,13 @@
         <v>294</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -26012,7 +26017,7 @@
         <v>153</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -26039,7 +26044,7 @@
         <v>83</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>83</v>
@@ -26050,10 +26055,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26171,10 +26176,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26294,10 +26299,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26419,10 +26424,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26445,13 +26450,13 @@
         <v>83</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -26502,7 +26507,7 @@
         <v>83</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>91</v>
@@ -26526,24 +26531,24 @@
         <v>83</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>470</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26569,13 +26574,13 @@
         <v>111</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26604,10 +26609,10 @@
         <v>174</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>83</v>
@@ -26625,7 +26630,7 @@
         <v>83</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -26652,7 +26657,7 @@
         <v>83</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AP193" t="s" s="2">
         <v>83</v>
@@ -26663,10 +26668,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26692,13 +26697,13 @@
         <v>180</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26727,10 +26732,10 @@
         <v>396</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>83</v>
@@ -26748,7 +26753,7 @@
         <v>83</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -26786,10 +26791,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26815,10 +26820,10 @@
         <v>208</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26869,7 +26874,7 @@
         <v>83</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -26907,13 +26912,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>83</v>
@@ -26938,13 +26943,13 @@
         <v>294</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26994,7 +26999,7 @@
         <v>83</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -27021,7 +27026,7 @@
         <v>83</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>83</v>
@@ -27032,10 +27037,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27153,10 +27158,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27276,10 +27281,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -27401,10 +27406,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27427,13 +27432,13 @@
         <v>83</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -27484,7 +27489,7 @@
         <v>83</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>91</v>
@@ -27499,33 +27504,33 @@
         <v>103</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>470</v>
       </c>
       <c r="AP200" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AQ200" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27551,13 +27556,13 @@
         <v>111</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -27586,10 +27591,10 @@
         <v>174</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>83</v>
@@ -27607,7 +27612,7 @@
         <v>83</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -27634,7 +27639,7 @@
         <v>83</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>83</v>
@@ -27645,10 +27650,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27674,13 +27679,13 @@
         <v>180</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -27709,10 +27714,10 @@
         <v>396</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>83</v>
@@ -27730,7 +27735,7 @@
         <v>83</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27768,10 +27773,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27797,10 +27802,10 @@
         <v>208</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -27851,7 +27856,7 @@
         <v>83</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27889,13 +27894,13 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D204" t="s" s="2">
         <v>83</v>
@@ -27920,13 +27925,13 @@
         <v>294</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -27976,7 +27981,7 @@
         <v>83</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -28003,7 +28008,7 @@
         <v>83</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>83</v>
@@ -28014,10 +28019,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28135,10 +28140,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28258,10 +28263,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28383,10 +28388,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28409,13 +28414,13 @@
         <v>83</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -28466,7 +28471,7 @@
         <v>83</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>91</v>
@@ -28481,33 +28486,33 @@
         <v>103</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>470</v>
       </c>
       <c r="AP208" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AQ208" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28533,13 +28538,13 @@
         <v>111</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
@@ -28568,10 +28573,10 @@
         <v>174</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>83</v>
@@ -28589,7 +28594,7 @@
         <v>83</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28616,7 +28621,7 @@
         <v>83</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>83</v>
@@ -28627,10 +28632,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28656,13 +28661,13 @@
         <v>180</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28691,10 +28696,10 @@
         <v>396</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>83</v>
@@ -28712,7 +28717,7 @@
         <v>83</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -28750,10 +28755,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28779,10 +28784,10 @@
         <v>208</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -28833,7 +28838,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28871,10 +28876,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28897,13 +28902,13 @@
         <v>83</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -28954,7 +28959,7 @@
         <v>83</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -28969,33 +28974,33 @@
         <v>103</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>469</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ212" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29018,16 +29023,16 @@
         <v>83</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -29077,7 +29082,7 @@
         <v>83</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -29101,10 +29106,10 @@
         <v>83</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -898,7 +898,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-eie-27-433:If (45-2) is null or &gt; now then fixed value #planned {null}eie-27-434:If (45-2) is not null, &lt; now, field 70 null then fixed value #in-progress {null}eie-27-435:If (45-70) is not null then fixed value #finished {null}</t>
+eie-27-433:If (45-2) is null or &gt; now then fixed value #planned {true}eie-27-434:If (45-2) is not null, &lt; now, field 70 null then fixed value #in-progress {true}eie-27-435:If (45-70) is not null then fixed value #finished {true}</t>
   </si>
   <si>
     <t>435: fixed value = #finished when PTF - DISCHARGE DATE (45-70) if not null</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
